--- a/ML/DF7_simulacao_avancada_teste01.xlsx
+++ b/ML/DF7_simulacao_avancada_teste01.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,13 +459,13 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46082.06944444445</v>
+        <v>46087.70833333334</v>
       </c>
       <c r="B2" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5</v>
+        <v>1.6328</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -482,16 +482,16 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46082.07013888889</v>
+        <v>46087.70902777778</v>
       </c>
       <c r="B3" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5</v>
+        <v>1.6389</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -500,21 +500,21 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46082.07083333333</v>
+        <v>46087.70972222222</v>
       </c>
       <c r="B4" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4941</v>
+        <v>1.64</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -523,21 +523,21 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46082.07152777778</v>
+        <v>46087.71041666667</v>
       </c>
       <c r="B5" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4881</v>
+        <v>1.6432</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -546,21 +546,21 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46082.07222222222</v>
+        <v>46087.71111111111</v>
       </c>
       <c r="B6" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4876</v>
+        <v>1.6488</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -569,90 +569,90 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46082.07291666666</v>
+        <v>46087.71180555555</v>
       </c>
       <c r="B7" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4881</v>
+        <v>1.6501</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46082.07361111111</v>
+        <v>46087.7125</v>
       </c>
       <c r="B8" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4894</v>
+        <v>1.6503</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46082.07430555556</v>
+        <v>46087.71319444444</v>
       </c>
       <c r="B9" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4899</v>
+        <v>1.6503</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46082.075</v>
+        <v>46087.71388888889</v>
       </c>
       <c r="B10" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4899</v>
+        <v>1.6504</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -661,73 +661,73 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46082.07569444444</v>
+        <v>46087.71458333333</v>
       </c>
       <c r="B11" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4895</v>
+        <v>1.6509</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46082.07638888889</v>
+        <v>46087.71527777778</v>
       </c>
       <c r="B12" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="C12" t="n">
-        <v>1.484</v>
+        <v>1.6511</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46082.07708333333</v>
+        <v>46087.71597222222</v>
       </c>
       <c r="B13" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4799</v>
+        <v>1.6516</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>1.64</v>
@@ -735,16 +735,16 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46082.07777777778</v>
+        <v>46087.71666666667</v>
       </c>
       <c r="B14" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="C14" t="n">
-        <v>1.48</v>
+        <v>1.6521</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -758,16 +758,16 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46082.07847222222</v>
+        <v>46087.71736111111</v>
       </c>
       <c r="B15" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="C15" t="n">
-        <v>1.4806</v>
+        <v>1.6521</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -776,21 +776,21 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46082.07916666667</v>
+        <v>46087.71805555555</v>
       </c>
       <c r="B16" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="C16" t="n">
-        <v>1.4808</v>
+        <v>1.6522</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -804,16 +804,16 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46082.07986111111</v>
+        <v>46087.71875</v>
       </c>
       <c r="B17" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="C17" t="n">
-        <v>1.4812</v>
+        <v>1.6533</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -827,22 +827,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46082.08055555556</v>
+        <v>46087.71944444445</v>
       </c>
       <c r="B18" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="C18" t="n">
-        <v>1.4814</v>
+        <v>1.6535</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>1.67</v>
@@ -850,22 +850,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46082.08125</v>
+        <v>46087.72013888889</v>
       </c>
       <c r="B19" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="C19" t="n">
-        <v>1.4826</v>
+        <v>1.6544</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>1.67</v>
@@ -873,16 +873,16 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46082.08194444444</v>
+        <v>46087.72083333333</v>
       </c>
       <c r="B20" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="C20" t="n">
-        <v>1.4831</v>
+        <v>1.6537</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -896,16 +896,16 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46082.08263888889</v>
+        <v>46087.72152777778</v>
       </c>
       <c r="B21" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="C21" t="n">
-        <v>1.4774</v>
+        <v>1.6533</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -914,21 +914,21 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46082.08333333334</v>
+        <v>46087.72222222222</v>
       </c>
       <c r="B22" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="C22" t="n">
-        <v>1.4787</v>
+        <v>1.6538</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -942,16 +942,16 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46082.08402777778</v>
+        <v>46087.72291666667</v>
       </c>
       <c r="B23" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="C23" t="n">
-        <v>1.4783</v>
+        <v>1.6557</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -960,21 +960,21 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46082.08472222222</v>
+        <v>46087.72361111111</v>
       </c>
       <c r="B24" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="C24" t="n">
-        <v>1.4815</v>
+        <v>1.6586</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -983,21 +983,21 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46082.08541666667</v>
+        <v>46087.72430555556</v>
       </c>
       <c r="B25" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="C25" t="n">
-        <v>1.4832</v>
+        <v>1.6601</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1006,21 +1006,21 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46082.08611111111</v>
+        <v>46087.725</v>
       </c>
       <c r="B26" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="C26" t="n">
-        <v>1.4768</v>
+        <v>1.6604</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1029,21 +1029,21 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46082.08680555555</v>
+        <v>46087.72569444445</v>
       </c>
       <c r="B27" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="C27" t="n">
-        <v>1.4762</v>
+        <v>1.6606</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1052,165 +1052,165 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46082.0875</v>
+        <v>46087.72638888889</v>
       </c>
       <c r="B28" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="C28" t="n">
-        <v>1.478</v>
+        <v>1.6615</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46082.08819444444</v>
+        <v>46087.72708333333</v>
       </c>
       <c r="B29" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="C29" t="n">
-        <v>1.4794</v>
+        <v>1.6612</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46082.08888888889</v>
+        <v>46087.72777777778</v>
       </c>
       <c r="B30" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="C30" t="n">
-        <v>1.48</v>
+        <v>1.662</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46082.08958333333</v>
+        <v>46087.72847222222</v>
       </c>
       <c r="B31" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="C31" t="n">
-        <v>1.486</v>
+        <v>1.6632</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46082.09027777778</v>
+        <v>46087.72916666666</v>
       </c>
       <c r="B32" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="C32" t="n">
-        <v>1.4902</v>
+        <v>1.6673</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46082.09097222222</v>
+        <v>46087.72986111111</v>
       </c>
       <c r="B33" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="C33" t="n">
-        <v>1.4922</v>
+        <v>1.6667</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46082.09166666667</v>
+        <v>46087.73055555556</v>
       </c>
       <c r="B34" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="C34" t="n">
-        <v>1.4919</v>
+        <v>1.6689</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
         <v>1.64</v>
@@ -1218,16 +1218,16 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46082.09236111111</v>
+        <v>46087.73125</v>
       </c>
       <c r="B35" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="C35" t="n">
-        <v>1.4918</v>
+        <v>1.6707</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -1236,21 +1236,21 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46082.09305555555</v>
+        <v>46087.73194444444</v>
       </c>
       <c r="B36" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="C36" t="n">
-        <v>1.4918</v>
+        <v>1.6715</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -1259,21 +1259,21 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46082.09375</v>
+        <v>46087.73263888889</v>
       </c>
       <c r="B37" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="C37" t="n">
-        <v>1.4924</v>
+        <v>1.6713</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -1287,16 +1287,16 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46082.09444444445</v>
+        <v>46087.73333333333</v>
       </c>
       <c r="B38" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="C38" t="n">
-        <v>1.4956</v>
+        <v>1.6696</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -1305,27 +1305,27 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46082.09513888889</v>
+        <v>46087.73402777778</v>
       </c>
       <c r="B39" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="C39" t="n">
-        <v>1.5048</v>
+        <v>1.673</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
         <v>1.67</v>
@@ -1333,22 +1333,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46082.09583333333</v>
+        <v>46087.73472222222</v>
       </c>
       <c r="B40" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="C40" t="n">
-        <v>1.5074</v>
+        <v>1.675</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
         <v>1.67</v>
@@ -1356,16 +1356,16 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46082.09652777778</v>
+        <v>46087.73541666667</v>
       </c>
       <c r="B41" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="C41" t="n">
-        <v>1.5109</v>
+        <v>1.6747</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -1379,16 +1379,16 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46082.09722222222</v>
+        <v>46087.73611111111</v>
       </c>
       <c r="B42" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="C42" t="n">
-        <v>1.5102</v>
+        <v>1.6773</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -1402,16 +1402,16 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46082.09791666667</v>
+        <v>46087.73680555556</v>
       </c>
       <c r="B43" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="C43" t="n">
-        <v>1.5118</v>
+        <v>1.6801</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -1425,16 +1425,16 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46082.09861111111</v>
+        <v>46087.7375</v>
       </c>
       <c r="B44" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="C44" t="n">
-        <v>1.5118</v>
+        <v>1.68</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -1443,21 +1443,21 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46082.09930555556</v>
+        <v>46087.73819444444</v>
       </c>
       <c r="B45" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="C45" t="n">
-        <v>1.5118</v>
+        <v>1.6796</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -1466,21 +1466,21 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46082.1</v>
+        <v>46087.73888888889</v>
       </c>
       <c r="B46" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="C46" t="n">
-        <v>1.5118</v>
+        <v>1.6784</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -1489,21 +1489,21 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46082.10069444445</v>
+        <v>46087.73958333334</v>
       </c>
       <c r="B47" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="C47" t="n">
-        <v>1.5118</v>
+        <v>1.6785</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -1512,21 +1512,21 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46082.10138888889</v>
+        <v>46087.74027777778</v>
       </c>
       <c r="B48" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="C48" t="n">
-        <v>1.5126</v>
+        <v>1.6802</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -1535,67 +1535,67 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46082.10208333333</v>
+        <v>46087.74097222222</v>
       </c>
       <c r="B49" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="C49" t="n">
-        <v>1.5126</v>
+        <v>1.6805</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46082.10277777778</v>
+        <v>46087.74166666667</v>
       </c>
       <c r="B50" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="C50" t="n">
-        <v>1.5158</v>
+        <v>1.681</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46082.10347222222</v>
+        <v>46087.74236111111</v>
       </c>
       <c r="B51" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="C51" t="n">
-        <v>1.5173</v>
+        <v>1.6814</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -1604,67 +1604,67 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46082.10416666666</v>
+        <v>46087.74305555555</v>
       </c>
       <c r="B52" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="C52" t="n">
-        <v>1.5208</v>
+        <v>1.6825</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46082.10486111111</v>
+        <v>46087.74375</v>
       </c>
       <c r="B53" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="C53" t="n">
-        <v>1.5296</v>
+        <v>1.6778</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46082.10555555556</v>
+        <v>46087.74444444444</v>
       </c>
       <c r="B54" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="C54" t="n">
-        <v>1.5302</v>
+        <v>1.6773</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
@@ -1678,16 +1678,16 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46082.10625</v>
+        <v>46087.74513888889</v>
       </c>
       <c r="B55" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="C55" t="n">
-        <v>1.5345</v>
+        <v>1.6776</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
@@ -1696,21 +1696,21 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46082.10694444444</v>
+        <v>46087.74583333333</v>
       </c>
       <c r="B56" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="C56" t="n">
-        <v>1.5373</v>
+        <v>1.6759</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>1</v>
@@ -1719,21 +1719,21 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46082.10763888889</v>
+        <v>46087.74652777778</v>
       </c>
       <c r="B57" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="C57" t="n">
-        <v>1.5427</v>
+        <v>1.6766</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -1742,73 +1742,73 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46082.10833333333</v>
+        <v>46087.74722222222</v>
       </c>
       <c r="B58" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="C58" t="n">
-        <v>1.5476</v>
+        <v>1.6784</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46082.10902777778</v>
+        <v>46087.74791666667</v>
       </c>
       <c r="B59" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="C59" t="n">
-        <v>1.5552</v>
+        <v>1.6792</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46082.10972222222</v>
+        <v>46087.74861111111</v>
       </c>
       <c r="B60" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="C60" t="n">
-        <v>1.5576</v>
+        <v>1.6792</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
         <v>1.67</v>
@@ -1816,22 +1816,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46082.11041666667</v>
+        <v>46087.74930555555</v>
       </c>
       <c r="B61" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="C61" t="n">
-        <v>1.5639</v>
+        <v>1.6793</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" t="n">
         <v>1.67</v>
@@ -1839,16 +1839,16 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46082.11111111111</v>
+        <v>46087.75</v>
       </c>
       <c r="B62" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="C62" t="n">
-        <v>1.5688</v>
+        <v>1.6783</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -1857,21 +1857,21 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46082.11180555556</v>
+        <v>46087.75069444445</v>
       </c>
       <c r="B63" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="C63" t="n">
-        <v>1.5713</v>
+        <v>1.6794</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -1880,21 +1880,21 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46082.1125</v>
+        <v>46087.75138888889</v>
       </c>
       <c r="B64" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="C64" t="n">
-        <v>1.573</v>
+        <v>1.6793</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -1908,16 +1908,16 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46082.11319444444</v>
+        <v>46087.75208333333</v>
       </c>
       <c r="B65" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="C65" t="n">
-        <v>1.5827</v>
+        <v>1.6787</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -1931,16 +1931,16 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46082.11388888889</v>
+        <v>46087.75277777778</v>
       </c>
       <c r="B66" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="C66" t="n">
-        <v>1.5883</v>
+        <v>1.6769</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -1949,21 +1949,21 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46082.11458333334</v>
+        <v>46087.75347222222</v>
       </c>
       <c r="B67" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="C67" t="n">
-        <v>1.5914</v>
+        <v>1.677</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -1977,16 +1977,16 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46082.11527777778</v>
+        <v>46087.75416666667</v>
       </c>
       <c r="B68" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="C68" t="n">
-        <v>1.5962</v>
+        <v>1.6782</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -1995,21 +1995,21 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46082.11597222222</v>
+        <v>46087.75486111111</v>
       </c>
       <c r="B69" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="C69" t="n">
-        <v>1.6008</v>
+        <v>1.678</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -2018,21 +2018,21 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46082.11666666667</v>
+        <v>46087.75555555556</v>
       </c>
       <c r="B70" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="C70" t="n">
-        <v>1.6008</v>
+        <v>1.6781</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -2041,21 +2041,21 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46082.11736111111</v>
+        <v>46087.75625</v>
       </c>
       <c r="B71" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="C71" t="n">
-        <v>1.6009</v>
+        <v>1.678</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
@@ -2064,21 +2064,21 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46082.11805555555</v>
+        <v>46087.75694444445</v>
       </c>
       <c r="B72" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="C72" t="n">
-        <v>1.601</v>
+        <v>1.6776</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
         <v>1</v>
@@ -2087,21 +2087,21 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46082.11875</v>
+        <v>46087.75763888889</v>
       </c>
       <c r="B73" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="C73" t="n">
-        <v>1.6083</v>
+        <v>1.6771</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
         <v>1</v>
@@ -2110,21 +2110,21 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46082.11944444444</v>
+        <v>46087.75833333333</v>
       </c>
       <c r="B74" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="C74" t="n">
-        <v>1.61</v>
+        <v>1.6757</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -2133,21 +2133,21 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46082.12013888889</v>
+        <v>46087.75902777778</v>
       </c>
       <c r="B75" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="C75" t="n">
-        <v>1.6107</v>
+        <v>1.6743</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
         <v>1</v>
@@ -2156,21 +2156,21 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46082.12083333333</v>
+        <v>46087.75972222222</v>
       </c>
       <c r="B76" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="C76" t="n">
-        <v>1.611</v>
+        <v>1.6694</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
         <v>1</v>
@@ -2179,21 +2179,21 @@
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46082.12152777778</v>
+        <v>46087.76041666666</v>
       </c>
       <c r="B77" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="C77" t="n">
-        <v>1.6134</v>
+        <v>1.6624</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
         <v>1</v>
@@ -2202,119 +2202,119 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46082.12222222222</v>
+        <v>46087.76111111111</v>
       </c>
       <c r="B78" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="C78" t="n">
-        <v>1.6174</v>
+        <v>1.6582</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46082.12291666667</v>
+        <v>46087.76180555556</v>
       </c>
       <c r="B79" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="C79" t="n">
-        <v>1.6237</v>
+        <v>1.6566</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46082.12361111111</v>
+        <v>46087.7625</v>
       </c>
       <c r="B80" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="C80" t="n">
-        <v>1.6258</v>
+        <v>1.6483</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46082.12430555555</v>
+        <v>46087.76319444444</v>
       </c>
       <c r="B81" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="C81" t="n">
-        <v>1.6297</v>
+        <v>1.6482</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46082.125</v>
+        <v>46087.76388888889</v>
       </c>
       <c r="B82" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="C82" t="n">
-        <v>1.631</v>
+        <v>1.6469</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
         <v>1.66</v>
@@ -2322,39 +2322,39 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46082.12569444445</v>
+        <v>46087.76458333333</v>
       </c>
       <c r="B83" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="C83" t="n">
-        <v>1.634</v>
+        <v>1.6453</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46082.12638888889</v>
+        <v>46087.76527777778</v>
       </c>
       <c r="B84" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="C84" t="n">
-        <v>1.6391</v>
+        <v>1.6452</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -2363,21 +2363,21 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46082.12708333333</v>
+        <v>46087.76597222222</v>
       </c>
       <c r="B85" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="C85" t="n">
-        <v>1.64</v>
+        <v>1.6446</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -2391,16 +2391,16 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46082.12777777778</v>
+        <v>46087.76666666667</v>
       </c>
       <c r="B86" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="C86" t="n">
-        <v>1.643</v>
+        <v>1.6422</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -2409,21 +2409,21 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46082.12847222222</v>
+        <v>46087.76736111111</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="C87" t="n">
-        <v>1.6501</v>
+        <v>1.6362</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -2432,21 +2432,21 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46082.12916666667</v>
+        <v>46087.76805555556</v>
       </c>
       <c r="B88" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="C88" t="n">
-        <v>1.654</v>
+        <v>1.64</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -2460,16 +2460,16 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46082.12986111111</v>
+        <v>46087.76875</v>
       </c>
       <c r="B89" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="C89" t="n">
-        <v>1.6554</v>
+        <v>1.6344</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -2478,24 +2478,24 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46082.13055555556</v>
+        <v>46087.76944444444</v>
       </c>
       <c r="B90" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="C90" t="n">
-        <v>1.6571</v>
+        <v>1.6386</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -2506,39 +2506,39 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46082.13125</v>
+        <v>46087.77013888889</v>
       </c>
       <c r="B91" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="C91" t="n">
-        <v>1.6586</v>
+        <v>1.6343</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46082.13194444445</v>
+        <v>46087.77083333334</v>
       </c>
       <c r="B92" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="C92" t="n">
-        <v>1.6655</v>
+        <v>1.6363</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
         <v>1</v>
@@ -2547,21 +2547,21 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46082.13263888889</v>
+        <v>46087.77222222222</v>
       </c>
       <c r="B93" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="C93" t="n">
-        <v>1.6667</v>
+        <v>1.6335</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
         <v>1</v>
@@ -2570,21 +2570,21 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>1.64</v>
+        <v>1.625</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46082.13333333333</v>
+        <v>46087.77291666667</v>
       </c>
       <c r="B94" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="C94" t="n">
-        <v>1.6695</v>
+        <v>1.6357</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -2593,21 +2593,21 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46082.13402777778</v>
+        <v>46087.77361111111</v>
       </c>
       <c r="B95" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="C95" t="n">
-        <v>1.6726</v>
+        <v>1.6338</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
@@ -2616,21 +2616,21 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46082.13472222222</v>
+        <v>46087.77430555555</v>
       </c>
       <c r="B96" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="C96" t="n">
-        <v>1.6706</v>
+        <v>1.6329</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
         <v>1</v>
@@ -2639,21 +2639,21 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46082.13541666666</v>
+        <v>46087.775</v>
       </c>
       <c r="B97" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="C97" t="n">
-        <v>1.6733</v>
+        <v>1.634</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
         <v>1</v>
@@ -2662,96 +2662,96 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46082.13611111111</v>
+        <v>46087.77569444444</v>
       </c>
       <c r="B98" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="C98" t="n">
-        <v>1.6716</v>
+        <v>1.6329</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46082.13680555556</v>
+        <v>46087.77638888889</v>
       </c>
       <c r="B99" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="C99" t="n">
-        <v>1.6752</v>
+        <v>1.6308</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46082.1375</v>
+        <v>46087.77708333333</v>
       </c>
       <c r="B100" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="C100" t="n">
-        <v>1.6702</v>
+        <v>1.6234</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46082.13819444444</v>
+        <v>46087.77777777778</v>
       </c>
       <c r="B101" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="C101" t="n">
-        <v>1.6709</v>
+        <v>1.6202</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" t="n">
         <v>1.66</v>
@@ -2759,22 +2759,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46082.13888888889</v>
+        <v>46087.77847222222</v>
       </c>
       <c r="B102" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="C102" t="n">
-        <v>1.6697</v>
+        <v>1.62</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" t="n">
         <v>1.66</v>
@@ -2782,62 +2782,62 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46082.13958333333</v>
+        <v>46087.77916666667</v>
       </c>
       <c r="B103" t="n">
         <v>1.59</v>
       </c>
       <c r="C103" t="n">
-        <v>1.6697</v>
+        <v>1.6137</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46082.14027777778</v>
+        <v>46087.77986111111</v>
       </c>
       <c r="B104" t="n">
         <v>1.59</v>
       </c>
       <c r="C104" t="n">
-        <v>1.6695</v>
+        <v>1.609</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46082.14097222222</v>
+        <v>46087.78055555555</v>
       </c>
       <c r="B105" t="n">
         <v>1.59</v>
       </c>
       <c r="C105" t="n">
-        <v>1.6672</v>
+        <v>1.6027</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
@@ -2851,16 +2851,16 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46082.14166666667</v>
+        <v>46087.78125</v>
       </c>
       <c r="B106" t="n">
         <v>1.59</v>
       </c>
       <c r="C106" t="n">
-        <v>1.6662</v>
+        <v>1.6028</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -2869,21 +2869,21 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46082.14236111111</v>
+        <v>46087.78194444445</v>
       </c>
       <c r="B107" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="C107" t="n">
-        <v>1.6654</v>
+        <v>1.6013</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
@@ -2892,21 +2892,21 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46082.14305555556</v>
+        <v>46087.78263888889</v>
       </c>
       <c r="B108" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="C108" t="n">
-        <v>1.6704</v>
+        <v>1.5939</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
@@ -2920,16 +2920,16 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46082.14375</v>
+        <v>46087.78333333333</v>
       </c>
       <c r="B109" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="C109" t="n">
-        <v>1.6763</v>
+        <v>1.5963</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
@@ -2938,21 +2938,21 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46082.14444444444</v>
+        <v>46087.78402777778</v>
       </c>
       <c r="B110" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="C110" t="n">
-        <v>1.6703</v>
+        <v>1.5962</v>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
@@ -2966,16 +2966,16 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46082.14513888889</v>
+        <v>46087.78472222222</v>
       </c>
       <c r="B111" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="C111" t="n">
-        <v>1.6701</v>
+        <v>1.5967</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
@@ -2989,16 +2989,16 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46082.14583333334</v>
+        <v>46087.78541666667</v>
       </c>
       <c r="B112" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="C112" t="n">
-        <v>1.6698</v>
+        <v>1.5964</v>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
         <v>1</v>
@@ -3007,21 +3007,21 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46082.14722222222</v>
+        <v>46087.78611111111</v>
       </c>
       <c r="B113" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="C113" t="n">
-        <v>1.6698</v>
+        <v>1.5926</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
         <v>1</v>
@@ -3030,67 +3030,67 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46082.14791666667</v>
+        <v>46087.78680555556</v>
       </c>
       <c r="B114" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="C114" t="n">
-        <v>1.6707</v>
+        <v>1.593</v>
       </c>
       <c r="D114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" t="n">
         <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46082.14861111111</v>
+        <v>46087.7875</v>
       </c>
       <c r="B115" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="C115" t="n">
-        <v>1.6704</v>
+        <v>1.5939</v>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
         <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46082.14930555555</v>
+        <v>46087.78819444445</v>
       </c>
       <c r="B116" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="C116" t="n">
-        <v>1.6654</v>
+        <v>1.592</v>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -3099,21 +3099,21 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46082.15</v>
+        <v>46087.78888888889</v>
       </c>
       <c r="B117" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="C117" t="n">
-        <v>1.6606</v>
+        <v>1.5839</v>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E117" t="n">
         <v>1</v>
@@ -3122,21 +3122,21 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46082.15069444444</v>
+        <v>46087.78958333333</v>
       </c>
       <c r="B118" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="C118" t="n">
-        <v>1.6588</v>
+        <v>1.5863</v>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E118" t="n">
         <v>1</v>
@@ -3145,182 +3145,182 @@
         <v>1</v>
       </c>
       <c r="G118" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46082.15138888889</v>
+        <v>46087.79027777778</v>
       </c>
       <c r="B119" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="C119" t="n">
-        <v>1.6603</v>
+        <v>1.5802</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46082.15208333333</v>
+        <v>46087.79097222222</v>
       </c>
       <c r="B120" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="C120" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46082.15277777778</v>
+        <v>46087.79166666666</v>
       </c>
       <c r="B121" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="C121" t="n">
-        <v>1.6598</v>
+        <v>1.5768</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46082.15347222222</v>
+        <v>46087.79236111111</v>
       </c>
       <c r="B122" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="C122" t="n">
-        <v>1.6542</v>
+        <v>1.5775</v>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46082.15416666667</v>
+        <v>46087.79305555556</v>
       </c>
       <c r="B123" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="C123" t="n">
-        <v>1.6512</v>
+        <v>1.5722</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46082.15486111111</v>
+        <v>46087.79375</v>
       </c>
       <c r="B124" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="C124" t="n">
-        <v>1.6503</v>
+        <v>1.5682</v>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46082.15555555555</v>
+        <v>46087.79444444444</v>
       </c>
       <c r="B125" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="C125" t="n">
-        <v>1.6501</v>
+        <v>1.5673</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46082.15625</v>
+        <v>46087.79513888889</v>
       </c>
       <c r="B126" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="C126" t="n">
-        <v>1.6476</v>
+        <v>1.5671</v>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
@@ -3329,21 +3329,21 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46082.15694444445</v>
+        <v>46087.79583333333</v>
       </c>
       <c r="B127" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="C127" t="n">
-        <v>1.6487</v>
+        <v>1.5642</v>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
@@ -3357,16 +3357,16 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46082.15763888889</v>
+        <v>46087.79652777778</v>
       </c>
       <c r="B128" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="C128" t="n">
-        <v>1.6428</v>
+        <v>1.5632</v>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
@@ -3375,21 +3375,21 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46082.15833333333</v>
+        <v>46087.79722222222</v>
       </c>
       <c r="B129" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="C129" t="n">
-        <v>1.6433</v>
+        <v>1.562</v>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
@@ -3403,16 +3403,16 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46082.15902777778</v>
+        <v>46087.79791666667</v>
       </c>
       <c r="B130" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="C130" t="n">
-        <v>1.6418</v>
+        <v>1.5568</v>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
@@ -3426,16 +3426,16 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46082.15972222222</v>
+        <v>46087.79861111111</v>
       </c>
       <c r="B131" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="C131" t="n">
-        <v>1.6401</v>
+        <v>1.5567</v>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
@@ -3449,16 +3449,16 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46082.16041666667</v>
+        <v>46087.79930555556</v>
       </c>
       <c r="B132" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="C132" t="n">
-        <v>1.6404</v>
+        <v>1.553</v>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
@@ -3472,39 +3472,39 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46082.16111111111</v>
+        <v>46087.8</v>
       </c>
       <c r="B133" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="C133" t="n">
-        <v>1.6399</v>
+        <v>1.5533</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46082.16180555556</v>
+        <v>46087.80069444444</v>
       </c>
       <c r="B134" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="C134" t="n">
-        <v>1.64</v>
+        <v>1.5517</v>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134" t="n">
         <v>1</v>
@@ -3513,21 +3513,21 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46082.1625</v>
+        <v>46087.80138888889</v>
       </c>
       <c r="B135" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="C135" t="n">
-        <v>1.6396</v>
+        <v>1.5506</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" t="n">
         <v>1</v>
@@ -3536,44 +3536,44 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46082.16319444445</v>
+        <v>46087.80208333334</v>
       </c>
       <c r="B136" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="C136" t="n">
-        <v>1.6395</v>
+        <v>1.5509</v>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E136" t="n">
         <v>1</v>
       </c>
       <c r="F136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46082.16388888889</v>
+        <v>46087.80277777778</v>
       </c>
       <c r="B137" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="C137" t="n">
-        <v>1.6395</v>
+        <v>1.5504</v>
       </c>
       <c r="D137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137" t="n">
         <v>1</v>
@@ -3582,21 +3582,21 @@
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46082.16458333333</v>
+        <v>46087.80347222222</v>
       </c>
       <c r="B138" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="C138" t="n">
-        <v>1.6374</v>
+        <v>1.5519</v>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E138" t="n">
         <v>1</v>
@@ -3605,21 +3605,21 @@
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46082.16527777778</v>
+        <v>46087.80416666667</v>
       </c>
       <c r="B139" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="C139" t="n">
-        <v>1.6317</v>
+        <v>1.5524</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E139" t="n">
         <v>1</v>
@@ -3628,119 +3628,119 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46082.16597222222</v>
+        <v>46087.80486111111</v>
       </c>
       <c r="B140" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="C140" t="n">
-        <v>1.6313</v>
+        <v>1.5512</v>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" t="n">
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46082.16666666666</v>
+        <v>46087.80555555555</v>
       </c>
       <c r="B141" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="C141" t="n">
-        <v>1.6298</v>
+        <v>1.5509</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46082.16736111111</v>
+        <v>46087.80625</v>
       </c>
       <c r="B142" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="C142" t="n">
-        <v>1.6298</v>
+        <v>1.559</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46082.16805555556</v>
+        <v>46087.80694444444</v>
       </c>
       <c r="B143" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="C143" t="n">
-        <v>1.6298</v>
+        <v>1.56</v>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46082.16875</v>
+        <v>46087.80763888889</v>
       </c>
       <c r="B144" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="C144" t="n">
-        <v>1.6286</v>
+        <v>1.56</v>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" t="n">
         <v>1.66</v>
@@ -3748,25 +3748,2233 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46082.16944444444</v>
+        <v>46087.80833333333</v>
       </c>
       <c r="B145" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1.5601</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>46087.80902777778</v>
+      </c>
+      <c r="B146" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1.5598</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>46087.80972222222</v>
+      </c>
+      <c r="B147" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1.5599</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>46087.81041666667</v>
+      </c>
+      <c r="B148" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1.5606</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>46087.81111111111</v>
+      </c>
+      <c r="B149" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C149" t="n">
+        <v>1.5616</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>46087.81180555555</v>
+      </c>
+      <c r="B150" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1.5696</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>46087.8125</v>
+      </c>
+      <c r="B151" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>46087.81319444445</v>
+      </c>
+      <c r="B152" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1.5706</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>46087.81388888889</v>
+      </c>
+      <c r="B153" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C153" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>46087.81458333333</v>
+      </c>
+      <c r="B154" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>46087.81527777778</v>
+      </c>
+      <c r="B155" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1.5715</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>46087.81597222222</v>
+      </c>
+      <c r="B156" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1.5742</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>46087.81666666667</v>
+      </c>
+      <c r="B157" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1.5772</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>46087.81736111111</v>
+      </c>
+      <c r="B158" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C158" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>46087.81805555556</v>
+      </c>
+      <c r="B159" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1.5808</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>46087.81875</v>
+      </c>
+      <c r="B160" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C160" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>46087.81944444445</v>
+      </c>
+      <c r="B161" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C161" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>46087.82013888889</v>
+      </c>
+      <c r="B162" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C162" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>46087.82083333333</v>
+      </c>
+      <c r="B163" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1.5889</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>46087.82152777778</v>
+      </c>
+      <c r="B164" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>46087.82222222222</v>
+      </c>
+      <c r="B165" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1.5932</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46087.82291666666</v>
+      </c>
+      <c r="B166" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1.5994</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>46087.82361111111</v>
+      </c>
+      <c r="B167" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1.6009</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" t="n">
         <v>1.68</v>
       </c>
-      <c r="C145" t="n">
-        <v>1.6287</v>
-      </c>
-      <c r="D145" t="n">
-        <v>1</v>
-      </c>
-      <c r="E145" t="n">
-        <v>0</v>
-      </c>
-      <c r="F145" t="n">
-        <v>0</v>
-      </c>
-      <c r="G145" t="n">
-        <v>1.66</v>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>46087.82430555556</v>
+      </c>
+      <c r="B168" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1.6072</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>46087.825</v>
+      </c>
+      <c r="B169" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1.606</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>46087.82569444444</v>
+      </c>
+      <c r="B170" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C170" t="n">
+        <v>1.6065</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>46087.82638888889</v>
+      </c>
+      <c r="B171" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1.6072</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>46087.82708333333</v>
+      </c>
+      <c r="B172" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="C172" t="n">
+        <v>1.6086</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>46087.82777777778</v>
+      </c>
+      <c r="B173" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="C173" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>46087.82847222222</v>
+      </c>
+      <c r="B174" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>46087.82916666667</v>
+      </c>
+      <c r="B175" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="C175" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>46087.82986111111</v>
+      </c>
+      <c r="B176" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>46087.83055555556</v>
+      </c>
+      <c r="B177" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="n">
+        <v>1</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>46087.83125</v>
+      </c>
+      <c r="B178" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="C178" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>46087.83194444444</v>
+      </c>
+      <c r="B179" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C179" t="n">
+        <v>1.6101</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>46087.83263888889</v>
+      </c>
+      <c r="B180" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1.6155</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>46087.83333333334</v>
+      </c>
+      <c r="B181" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>46087.83402777778</v>
+      </c>
+      <c r="B182" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1.6202</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>46087.83472222222</v>
+      </c>
+      <c r="B183" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1.6207</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>46087.83541666667</v>
+      </c>
+      <c r="B184" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C184" t="n">
+        <v>1.6203</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46087.83611111111</v>
+      </c>
+      <c r="B185" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1.6213</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46087.83680555555</v>
+      </c>
+      <c r="B186" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1.6264</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>46087.8375</v>
+      </c>
+      <c r="B187" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1.6257</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" t="n">
+        <v>1</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>46087.83819444444</v>
+      </c>
+      <c r="B188" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C188" t="n">
+        <v>1.6301</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>46087.83888888889</v>
+      </c>
+      <c r="B189" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>46087.83958333333</v>
+      </c>
+      <c r="B190" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C190" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>46087.84027777778</v>
+      </c>
+      <c r="B191" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C191" t="n">
+        <v>1.6303</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>46087.84097222222</v>
+      </c>
+      <c r="B192" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C192" t="n">
+        <v>1.6317</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>46087.84166666667</v>
+      </c>
+      <c r="B193" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C193" t="n">
+        <v>1.634</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>46087.84236111111</v>
+      </c>
+      <c r="B194" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C194" t="n">
+        <v>1.6399</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>46087.84305555555</v>
+      </c>
+      <c r="B195" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C195" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>46087.84375</v>
+      </c>
+      <c r="B196" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C196" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>46087.84444444445</v>
+      </c>
+      <c r="B197" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1.6401</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>46087.84513888889</v>
+      </c>
+      <c r="B198" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1.6426</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>46087.84583333333</v>
+      </c>
+      <c r="B199" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C199" t="n">
+        <v>1.6488</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>46087.84652777778</v>
+      </c>
+      <c r="B200" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1.6507</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>46087.84722222222</v>
+      </c>
+      <c r="B201" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C201" t="n">
+        <v>1.6509</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>1</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>46087.84791666667</v>
+      </c>
+      <c r="B202" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C202" t="n">
+        <v>1.6502</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" t="n">
+        <v>1</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>46087.84861111111</v>
+      </c>
+      <c r="B203" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C203" t="n">
+        <v>1.6507</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" t="n">
+        <v>1</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>46087.84930555556</v>
+      </c>
+      <c r="B204" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C204" t="n">
+        <v>1.6518</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" t="n">
+        <v>1</v>
+      </c>
+      <c r="F204" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>46087.85</v>
+      </c>
+      <c r="B205" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C205" t="n">
+        <v>1.6532</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" t="n">
+        <v>1</v>
+      </c>
+      <c r="F205" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>46087.85069444445</v>
+      </c>
+      <c r="B206" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C206" t="n">
+        <v>1.6557</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>46087.85138888889</v>
+      </c>
+      <c r="B207" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C207" t="n">
+        <v>1.6567</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1</v>
+      </c>
+      <c r="F207" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>46087.85208333333</v>
+      </c>
+      <c r="B208" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C208" t="n">
+        <v>1.6586</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>46087.85277777778</v>
+      </c>
+      <c r="B209" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C209" t="n">
+        <v>1.6622</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" t="n">
+        <v>1</v>
+      </c>
+      <c r="G209" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>46087.85347222222</v>
+      </c>
+      <c r="B210" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C210" t="n">
+        <v>1.6601</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>46087.85416666666</v>
+      </c>
+      <c r="B211" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C211" t="n">
+        <v>1.6642</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>46087.85486111111</v>
+      </c>
+      <c r="B212" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C212" t="n">
+        <v>1.6653</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46087.85555555556</v>
+      </c>
+      <c r="B213" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C213" t="n">
+        <v>1.6694</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46087.85625</v>
+      </c>
+      <c r="B214" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C214" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46087.85694444444</v>
+      </c>
+      <c r="B215" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C215" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46087.85763888889</v>
+      </c>
+      <c r="B216" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C216" t="n">
+        <v>1.6703</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46087.85833333333</v>
+      </c>
+      <c r="B217" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C217" t="n">
+        <v>1.671</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46087.85902777778</v>
+      </c>
+      <c r="B218" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C218" t="n">
+        <v>1.6713</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46087.85972222222</v>
+      </c>
+      <c r="B219" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C219" t="n">
+        <v>1.6754</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46087.86041666667</v>
+      </c>
+      <c r="B220" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C220" t="n">
+        <v>1.679</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="n">
+        <v>1</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46087.86111111111</v>
+      </c>
+      <c r="B221" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C221" t="n">
+        <v>1.6788</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" t="n">
+        <v>1</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46087.86180555556</v>
+      </c>
+      <c r="B222" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C222" t="n">
+        <v>1.6777</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" t="n">
+        <v>1</v>
+      </c>
+      <c r="F222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46087.8625</v>
+      </c>
+      <c r="B223" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C223" t="n">
+        <v>1.6787</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" t="n">
+        <v>1</v>
+      </c>
+      <c r="F223" t="n">
+        <v>1</v>
+      </c>
+      <c r="G223" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46087.86319444444</v>
+      </c>
+      <c r="B224" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C224" t="n">
+        <v>1.6778</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" t="n">
+        <v>1</v>
+      </c>
+      <c r="F224" t="n">
+        <v>1</v>
+      </c>
+      <c r="G224" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46087.86388888889</v>
+      </c>
+      <c r="B225" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C225" t="n">
+        <v>1.6781</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" t="n">
+        <v>1</v>
+      </c>
+      <c r="F225" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46087.86458333334</v>
+      </c>
+      <c r="B226" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C226" t="n">
+        <v>1.6791</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="n">
+        <v>1</v>
+      </c>
+      <c r="F226" t="n">
+        <v>1</v>
+      </c>
+      <c r="G226" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46087.86527777778</v>
+      </c>
+      <c r="B227" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C227" t="n">
+        <v>1.6801</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" t="n">
+        <v>1</v>
+      </c>
+      <c r="F227" t="n">
+        <v>1</v>
+      </c>
+      <c r="G227" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46087.86597222222</v>
+      </c>
+      <c r="B228" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C228" t="n">
+        <v>1.6806</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0</v>
+      </c>
+      <c r="E228" t="n">
+        <v>1</v>
+      </c>
+      <c r="F228" t="n">
+        <v>1</v>
+      </c>
+      <c r="G228" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46087.86666666667</v>
+      </c>
+      <c r="B229" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C229" t="n">
+        <v>1.6819</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="n">
+        <v>1</v>
+      </c>
+      <c r="F229" t="n">
+        <v>1</v>
+      </c>
+      <c r="G229" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>46087.86736111111</v>
+      </c>
+      <c r="B230" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C230" t="n">
+        <v>1.6802</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1</v>
+      </c>
+      <c r="F230" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>46087.86805555555</v>
+      </c>
+      <c r="B231" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C231" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" t="n">
+        <v>1</v>
+      </c>
+      <c r="G231" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>46087.86875</v>
+      </c>
+      <c r="B232" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C232" t="n">
+        <v>1.6799</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>46087.86944444444</v>
+      </c>
+      <c r="B233" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C233" t="n">
+        <v>1.6798</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>46087.87013888889</v>
+      </c>
+      <c r="B234" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C234" t="n">
+        <v>1.6774</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0</v>
+      </c>
+      <c r="E234" t="n">
+        <v>0</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>46087.87083333333</v>
+      </c>
+      <c r="B235" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C235" t="n">
+        <v>1.6797</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>46087.87152777778</v>
+      </c>
+      <c r="B236" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C236" t="n">
+        <v>1.6779</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>46087.87222222222</v>
+      </c>
+      <c r="B237" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C237" t="n">
+        <v>1.6767</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0</v>
+      </c>
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>46087.87291666667</v>
+      </c>
+      <c r="B238" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C238" t="n">
+        <v>1.6758</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>46087.87361111111</v>
+      </c>
+      <c r="B239" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C239" t="n">
+        <v>1.6739</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>46087.87430555555</v>
+      </c>
+      <c r="B240" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C240" t="n">
+        <v>1.6709</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>1</v>
+      </c>
+      <c r="F240" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>46087.875</v>
+      </c>
+      <c r="B241" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C241" t="n">
+        <v>1.6645</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0</v>
+      </c>
+      <c r="E241" t="n">
+        <v>1</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" t="n">
+        <v>1.63</v>
       </c>
     </row>
   </sheetData>

--- a/ML/DF7_simulacao_avancada_teste01.xlsx
+++ b/ML/DF7_simulacao_avancada_teste01.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G241"/>
+  <dimension ref="A1:G357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,45 +459,45 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46087.70833333334</v>
+        <v>46102.58333333334</v>
       </c>
       <c r="B2" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="C2" t="n">
-        <v>1.6328</v>
+        <v>1.6612</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46087.70902777778</v>
+        <v>46102.58402777778</v>
       </c>
       <c r="B3" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6389</v>
+        <v>1.6611</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1.65</v>
@@ -505,22 +505,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46087.70972222222</v>
+        <v>46102.58472222222</v>
       </c>
       <c r="B4" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="C4" t="n">
-        <v>1.64</v>
+        <v>1.6617</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>1.65</v>
@@ -528,59 +528,59 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46087.71041666667</v>
+        <v>46102.58541666667</v>
       </c>
       <c r="B5" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6432</v>
+        <v>1.6642</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46087.71111111111</v>
+        <v>46102.58611111111</v>
       </c>
       <c r="B6" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6488</v>
+        <v>1.6685</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46087.71180555555</v>
+        <v>46102.58680555555</v>
       </c>
       <c r="B7" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6501</v>
+        <v>1.6707</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -589,21 +589,21 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46087.7125</v>
+        <v>46102.5875</v>
       </c>
       <c r="B8" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6503</v>
+        <v>1.6706</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -612,182 +612,182 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46087.71319444444</v>
+        <v>46102.58819444444</v>
       </c>
       <c r="B9" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="C9" t="n">
-        <v>1.6503</v>
+        <v>1.6717</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46087.71388888889</v>
+        <v>46102.58888888889</v>
       </c>
       <c r="B10" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6504</v>
+        <v>1.6712</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46087.71458333333</v>
+        <v>46102.58958333333</v>
       </c>
       <c r="B11" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="C11" t="n">
-        <v>1.6509</v>
+        <v>1.6742</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46087.71527777778</v>
+        <v>46102.59027777778</v>
       </c>
       <c r="B12" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="C12" t="n">
-        <v>1.6511</v>
+        <v>1.6754</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46087.71597222222</v>
+        <v>46102.59097222222</v>
       </c>
       <c r="B13" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="C13" t="n">
-        <v>1.6516</v>
+        <v>1.6804</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46087.71666666667</v>
+        <v>46102.59166666667</v>
       </c>
       <c r="B14" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="C14" t="n">
-        <v>1.6521</v>
+        <v>1.6805</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46087.71736111111</v>
+        <v>46102.59236111111</v>
       </c>
       <c r="B15" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="C15" t="n">
-        <v>1.6521</v>
+        <v>1.6803</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46087.71805555555</v>
+        <v>46102.59305555555</v>
       </c>
       <c r="B16" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6522</v>
+        <v>1.6812</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -796,21 +796,21 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46087.71875</v>
+        <v>46102.59375</v>
       </c>
       <c r="B17" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="C17" t="n">
-        <v>1.6533</v>
+        <v>1.6801</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -819,21 +819,21 @@
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46087.71944444445</v>
+        <v>46102.59444444445</v>
       </c>
       <c r="B18" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="C18" t="n">
-        <v>1.6535</v>
+        <v>1.6804</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -842,182 +842,182 @@
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46087.72013888889</v>
+        <v>46102.59513888889</v>
       </c>
       <c r="B19" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="C19" t="n">
-        <v>1.6544</v>
+        <v>1.68</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46087.72083333333</v>
+        <v>46102.59583333333</v>
       </c>
       <c r="B20" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="C20" t="n">
-        <v>1.6537</v>
+        <v>1.6802</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46087.72152777778</v>
+        <v>46102.59652777778</v>
       </c>
       <c r="B21" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="C21" t="n">
-        <v>1.6533</v>
+        <v>1.6802</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46087.72222222222</v>
+        <v>46102.59722222222</v>
       </c>
       <c r="B22" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="C22" t="n">
-        <v>1.6538</v>
+        <v>1.6804</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46087.72291666667</v>
+        <v>46102.59791666667</v>
       </c>
       <c r="B23" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="C23" t="n">
-        <v>1.6557</v>
+        <v>1.6803</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46087.72361111111</v>
+        <v>46102.59861111111</v>
       </c>
       <c r="B24" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="C24" t="n">
-        <v>1.6586</v>
+        <v>1.6807</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46087.72430555556</v>
+        <v>46102.59930555556</v>
       </c>
       <c r="B25" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="C25" t="n">
-        <v>1.6601</v>
+        <v>1.6814</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46087.725</v>
+        <v>46102.6</v>
       </c>
       <c r="B26" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="C26" t="n">
-        <v>1.6604</v>
+        <v>1.6806</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1026,21 +1026,21 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46087.72569444445</v>
+        <v>46102.60069444445</v>
       </c>
       <c r="B27" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="C27" t="n">
-        <v>1.6606</v>
+        <v>1.6802</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1052,165 +1052,165 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46087.72638888889</v>
+        <v>46102.60138888889</v>
       </c>
       <c r="B28" t="n">
         <v>1.66</v>
       </c>
       <c r="C28" t="n">
-        <v>1.6615</v>
+        <v>1.6802</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46087.72708333333</v>
+        <v>46102.60208333333</v>
       </c>
       <c r="B29" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="C29" t="n">
-        <v>1.6612</v>
+        <v>1.6807</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46087.72777777778</v>
+        <v>46102.60277777778</v>
       </c>
       <c r="B30" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="C30" t="n">
-        <v>1.662</v>
+        <v>1.6801</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46087.72847222222</v>
+        <v>46102.60347222222</v>
       </c>
       <c r="B31" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="C31" t="n">
-        <v>1.6632</v>
+        <v>1.6837</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46087.72916666666</v>
+        <v>46102.60416666666</v>
       </c>
       <c r="B32" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="C32" t="n">
-        <v>1.6673</v>
+        <v>1.6814</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46087.72986111111</v>
+        <v>46102.60486111111</v>
       </c>
       <c r="B33" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="C33" t="n">
-        <v>1.6667</v>
+        <v>1.6793</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46087.73055555556</v>
+        <v>46102.60555555556</v>
       </c>
       <c r="B34" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="C34" t="n">
-        <v>1.6689</v>
+        <v>1.6756</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>1.64</v>
@@ -1218,36 +1218,36 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46087.73125</v>
+        <v>46102.60625</v>
       </c>
       <c r="B35" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="C35" t="n">
-        <v>1.6707</v>
+        <v>1.6756</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46087.73194444444</v>
+        <v>46102.60694444444</v>
       </c>
       <c r="B36" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="C36" t="n">
-        <v>1.6715</v>
+        <v>1.6774</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1256,21 +1256,21 @@
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46087.73263888889</v>
+        <v>46102.60763888889</v>
       </c>
       <c r="B37" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="C37" t="n">
-        <v>1.6713</v>
+        <v>1.6767</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1279,21 +1279,21 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46087.73333333333</v>
+        <v>46102.60833333333</v>
       </c>
       <c r="B38" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="C38" t="n">
-        <v>1.6696</v>
+        <v>1.6761</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -1302,21 +1302,21 @@
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46087.73402777778</v>
+        <v>46102.60902777778</v>
       </c>
       <c r="B39" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="C39" t="n">
-        <v>1.673</v>
+        <v>1.6761</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -1328,179 +1328,179 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46087.73472222222</v>
+        <v>46102.60972222222</v>
       </c>
       <c r="B40" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="C40" t="n">
-        <v>1.675</v>
+        <v>1.6757</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46087.73541666667</v>
+        <v>46102.61041666667</v>
       </c>
       <c r="B41" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="C41" t="n">
-        <v>1.6747</v>
+        <v>1.6758</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46087.73611111111</v>
+        <v>46102.61111111111</v>
       </c>
       <c r="B42" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="C42" t="n">
-        <v>1.6773</v>
+        <v>1.6792</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46087.73680555556</v>
+        <v>46102.61180555556</v>
       </c>
       <c r="B43" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="C43" t="n">
-        <v>1.6801</v>
+        <v>1.6789</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46087.7375</v>
+        <v>46102.6125</v>
       </c>
       <c r="B44" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="C44" t="n">
-        <v>1.68</v>
+        <v>1.6784</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46087.73819444444</v>
+        <v>46102.61319444444</v>
       </c>
       <c r="B45" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="C45" t="n">
-        <v>1.6796</v>
+        <v>1.6786</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46087.73888888889</v>
+        <v>46102.61388888889</v>
       </c>
       <c r="B46" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="C46" t="n">
-        <v>1.6784</v>
+        <v>1.6775</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46087.73958333334</v>
+        <v>46102.61458333334</v>
       </c>
       <c r="B47" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="C47" t="n">
-        <v>1.6785</v>
+        <v>1.677</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -1509,21 +1509,21 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46087.74027777778</v>
+        <v>46102.61527777778</v>
       </c>
       <c r="B48" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="C48" t="n">
-        <v>1.6802</v>
+        <v>1.677</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -1535,142 +1535,142 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46087.74097222222</v>
+        <v>46102.61597222222</v>
       </c>
       <c r="B49" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="C49" t="n">
-        <v>1.6805</v>
+        <v>1.677</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46087.74166666667</v>
+        <v>46102.61666666667</v>
       </c>
       <c r="B50" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="C50" t="n">
-        <v>1.681</v>
+        <v>1.6761</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46087.74236111111</v>
+        <v>46102.61736111111</v>
       </c>
       <c r="B51" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="C51" t="n">
-        <v>1.6814</v>
+        <v>1.6761</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46087.74305555555</v>
+        <v>46102.61805555555</v>
       </c>
       <c r="B52" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="C52" t="n">
-        <v>1.6825</v>
+        <v>1.6753</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46087.74375</v>
+        <v>46102.61875</v>
       </c>
       <c r="B53" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="C53" t="n">
-        <v>1.6778</v>
+        <v>1.6753</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46087.74444444444</v>
+        <v>46102.61944444444</v>
       </c>
       <c r="B54" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="C54" t="n">
-        <v>1.6773</v>
+        <v>1.6753</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>1.64</v>
@@ -1678,22 +1678,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46087.74513888889</v>
+        <v>46102.62013888889</v>
       </c>
       <c r="B55" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="C55" t="n">
-        <v>1.6776</v>
+        <v>1.6752</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>1.64</v>
@@ -1701,13 +1701,13 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46087.74583333333</v>
+        <v>46102.62083333333</v>
       </c>
       <c r="B56" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="C56" t="n">
-        <v>1.6759</v>
+        <v>1.6798</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -1716,21 +1716,21 @@
         <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46087.74652777778</v>
+        <v>46102.62152777778</v>
       </c>
       <c r="B57" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="C57" t="n">
-        <v>1.6766</v>
+        <v>1.6795</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -1739,21 +1739,21 @@
         <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46087.74722222222</v>
+        <v>46102.62222222222</v>
       </c>
       <c r="B58" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="C58" t="n">
-        <v>1.6784</v>
+        <v>1.6795</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -1762,21 +1762,21 @@
         <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46087.74791666667</v>
+        <v>46102.62291666667</v>
       </c>
       <c r="B59" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="C59" t="n">
-        <v>1.6792</v>
+        <v>1.6795</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -1788,18 +1788,18 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46087.74861111111</v>
+        <v>46102.62361111111</v>
       </c>
       <c r="B60" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="C60" t="n">
-        <v>1.6792</v>
+        <v>1.6796</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -1811,18 +1811,18 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46087.74930555555</v>
+        <v>46102.62430555555</v>
       </c>
       <c r="B61" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="C61" t="n">
-        <v>1.6793</v>
+        <v>1.6796</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -1834,73 +1834,73 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46087.75</v>
+        <v>46102.625</v>
       </c>
       <c r="B62" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="C62" t="n">
-        <v>1.6783</v>
+        <v>1.6795</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46087.75069444445</v>
+        <v>46102.62569444445</v>
       </c>
       <c r="B63" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="C63" t="n">
-        <v>1.6794</v>
+        <v>1.6795</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46087.75138888889</v>
+        <v>46102.62638888889</v>
       </c>
       <c r="B64" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="C64" t="n">
-        <v>1.6793</v>
+        <v>1.6795</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
         <v>1.66</v>
@@ -1908,22 +1908,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46087.75208333333</v>
+        <v>46102.62708333333</v>
       </c>
       <c r="B65" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="C65" t="n">
-        <v>1.6787</v>
+        <v>1.6794</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
         <v>1.66</v>
@@ -1931,59 +1931,59 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46087.75277777778</v>
+        <v>46102.62777777778</v>
       </c>
       <c r="B66" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="C66" t="n">
-        <v>1.6769</v>
+        <v>1.6788</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46087.75347222222</v>
+        <v>46102.62847222222</v>
       </c>
       <c r="B67" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="C67" t="n">
-        <v>1.677</v>
+        <v>1.679</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46087.75416666667</v>
+        <v>46102.62916666667</v>
       </c>
       <c r="B68" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="C68" t="n">
-        <v>1.6782</v>
+        <v>1.679</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -1992,21 +1992,21 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46087.75486111111</v>
+        <v>46102.62986111111</v>
       </c>
       <c r="B69" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="C69" t="n">
-        <v>1.678</v>
+        <v>1.6791</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -2018,18 +2018,18 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46087.75555555556</v>
+        <v>46102.63055555556</v>
       </c>
       <c r="B70" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="C70" t="n">
-        <v>1.6781</v>
+        <v>1.6792</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -2041,133 +2041,133 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46087.75625</v>
+        <v>46102.63125</v>
       </c>
       <c r="B71" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="C71" t="n">
-        <v>1.678</v>
+        <v>1.6779</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46087.75694444445</v>
+        <v>46102.63194444445</v>
       </c>
       <c r="B72" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="C72" t="n">
-        <v>1.6776</v>
+        <v>1.6779</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46087.75763888889</v>
+        <v>46102.63263888889</v>
       </c>
       <c r="B73" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="C73" t="n">
-        <v>1.6771</v>
+        <v>1.6787</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46087.75833333333</v>
+        <v>46102.63333333333</v>
       </c>
       <c r="B74" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="C74" t="n">
-        <v>1.6757</v>
+        <v>1.6787</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46087.75902777778</v>
+        <v>46102.63402777778</v>
       </c>
       <c r="B75" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="C75" t="n">
-        <v>1.6743</v>
+        <v>1.6789</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46087.75972222222</v>
+        <v>46102.63472222222</v>
       </c>
       <c r="B76" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="C76" t="n">
-        <v>1.6694</v>
+        <v>1.6789</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -2176,21 +2176,21 @@
         <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46087.76041666666</v>
+        <v>46102.63541666666</v>
       </c>
       <c r="B77" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="C77" t="n">
-        <v>1.6624</v>
+        <v>1.6786</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -2199,21 +2199,21 @@
         <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46087.76111111111</v>
+        <v>46102.63611111111</v>
       </c>
       <c r="B78" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="C78" t="n">
-        <v>1.6582</v>
+        <v>1.6786</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -2222,21 +2222,21 @@
         <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46087.76180555556</v>
+        <v>46102.63680555556</v>
       </c>
       <c r="B79" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="C79" t="n">
-        <v>1.6566</v>
+        <v>1.6745</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -2245,21 +2245,21 @@
         <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46087.7625</v>
+        <v>46102.6375</v>
       </c>
       <c r="B80" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="C80" t="n">
-        <v>1.6483</v>
+        <v>1.6736</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -2271,18 +2271,18 @@
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46087.76319444444</v>
+        <v>46102.63819444444</v>
       </c>
       <c r="B81" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="C81" t="n">
-        <v>1.6482</v>
+        <v>1.6781</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -2294,18 +2294,18 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46087.76388888889</v>
+        <v>46102.63888888889</v>
       </c>
       <c r="B82" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="C82" t="n">
-        <v>1.6469</v>
+        <v>1.6788</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -2317,18 +2317,18 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46087.76458333333</v>
+        <v>46102.63958333333</v>
       </c>
       <c r="B83" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="C83" t="n">
-        <v>1.6453</v>
+        <v>1.6788</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -2340,73 +2340,73 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46087.76527777778</v>
+        <v>46102.64027777778</v>
       </c>
       <c r="B84" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="C84" t="n">
-        <v>1.6452</v>
+        <v>1.6788</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46087.76597222222</v>
+        <v>46102.64097222222</v>
       </c>
       <c r="B85" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="C85" t="n">
-        <v>1.6446</v>
+        <v>1.6787</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46087.76666666667</v>
+        <v>46102.64166666667</v>
       </c>
       <c r="B86" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="C86" t="n">
-        <v>1.6422</v>
+        <v>1.6787</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" t="n">
         <v>1.66</v>
@@ -2414,82 +2414,82 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46087.76736111111</v>
+        <v>46102.64236111111</v>
       </c>
       <c r="B87" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="C87" t="n">
-        <v>1.6362</v>
+        <v>1.678</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46087.76805555556</v>
+        <v>46102.64305555556</v>
       </c>
       <c r="B88" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="C88" t="n">
-        <v>1.64</v>
+        <v>1.6781</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46087.76875</v>
+        <v>46102.64375</v>
       </c>
       <c r="B89" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="C89" t="n">
-        <v>1.6344</v>
+        <v>1.6783</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46087.76944444444</v>
+        <v>46102.64444444444</v>
       </c>
       <c r="B90" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="C90" t="n">
-        <v>1.6386</v>
+        <v>1.6783</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -2501,18 +2501,18 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46087.77013888889</v>
+        <v>46102.64513888889</v>
       </c>
       <c r="B91" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="C91" t="n">
-        <v>1.6343</v>
+        <v>1.6783</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -2524,96 +2524,96 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46087.77083333334</v>
+        <v>46102.64583333334</v>
       </c>
       <c r="B92" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="C92" t="n">
-        <v>1.6363</v>
+        <v>1.6783</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46087.77222222222</v>
+        <v>46102.64930555555</v>
       </c>
       <c r="B93" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="C93" t="n">
-        <v>1.6335</v>
+        <v>1.6783</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>1.625</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46087.77291666667</v>
+        <v>46102.65</v>
       </c>
       <c r="B94" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="C94" t="n">
-        <v>1.6357</v>
+        <v>1.6783</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46087.77361111111</v>
+        <v>46102.65069444444</v>
       </c>
       <c r="B95" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="C95" t="n">
-        <v>1.6338</v>
+        <v>1.6781</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
         <v>1.63</v>
@@ -2621,13 +2621,13 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46087.77430555555</v>
+        <v>46102.65138888889</v>
       </c>
       <c r="B96" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="C96" t="n">
-        <v>1.6329</v>
+        <v>1.6785</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
         <v>1.63</v>
@@ -2644,13 +2644,13 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46087.775</v>
+        <v>46102.65208333333</v>
       </c>
       <c r="B97" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="C97" t="n">
-        <v>1.634</v>
+        <v>1.6785</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -2659,21 +2659,21 @@
         <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46087.77569444444</v>
+        <v>46102.65277777778</v>
       </c>
       <c r="B98" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="C98" t="n">
-        <v>1.6329</v>
+        <v>1.6744</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -2682,21 +2682,21 @@
         <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46087.77638888889</v>
+        <v>46102.65347222222</v>
       </c>
       <c r="B99" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="C99" t="n">
-        <v>1.6308</v>
+        <v>1.6753</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -2708,18 +2708,18 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46087.77708333333</v>
+        <v>46102.65416666667</v>
       </c>
       <c r="B100" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="C100" t="n">
-        <v>1.6234</v>
+        <v>1.6785</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -2731,18 +2731,18 @@
         <v>1</v>
       </c>
       <c r="G100" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46087.77777777778</v>
+        <v>46102.65486111111</v>
       </c>
       <c r="B101" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="C101" t="n">
-        <v>1.6202</v>
+        <v>1.6785</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -2754,18 +2754,18 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46087.77847222222</v>
+        <v>46102.65555555555</v>
       </c>
       <c r="B102" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="C102" t="n">
-        <v>1.62</v>
+        <v>1.6789</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -2777,18 +2777,18 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46087.77916666667</v>
+        <v>46102.65625</v>
       </c>
       <c r="B103" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="C103" t="n">
-        <v>1.6137</v>
+        <v>1.6789</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -2800,50 +2800,50 @@
         <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46087.77986111111</v>
+        <v>46102.65694444445</v>
       </c>
       <c r="B104" t="n">
         <v>1.59</v>
       </c>
       <c r="C104" t="n">
-        <v>1.609</v>
+        <v>1.6788</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" t="n">
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46087.78055555555</v>
+        <v>46102.65763888889</v>
       </c>
       <c r="B105" t="n">
         <v>1.59</v>
       </c>
       <c r="C105" t="n">
-        <v>1.6027</v>
+        <v>1.6788</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105" t="n">
         <v>1.66</v>
@@ -2851,59 +2851,59 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46087.78125</v>
+        <v>46102.65833333333</v>
       </c>
       <c r="B106" t="n">
         <v>1.59</v>
       </c>
       <c r="C106" t="n">
-        <v>1.6028</v>
+        <v>1.6781</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46087.78194444445</v>
+        <v>46102.65902777778</v>
       </c>
       <c r="B107" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="C107" t="n">
-        <v>1.6013</v>
+        <v>1.6783</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46087.78263888889</v>
+        <v>46102.65972222222</v>
       </c>
       <c r="B108" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="C108" t="n">
-        <v>1.5939</v>
+        <v>1.6783</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -2912,21 +2912,21 @@
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46087.78333333333</v>
+        <v>46102.66041666667</v>
       </c>
       <c r="B109" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="C109" t="n">
-        <v>1.5963</v>
+        <v>1.6783</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -2938,18 +2938,18 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46087.78402777778</v>
+        <v>46102.66111111111</v>
       </c>
       <c r="B110" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="C110" t="n">
-        <v>1.5962</v>
+        <v>1.6781</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -2961,18 +2961,18 @@
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46087.78472222222</v>
+        <v>46102.66180555556</v>
       </c>
       <c r="B111" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="C111" t="n">
-        <v>1.5967</v>
+        <v>1.6781</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -2984,119 +2984,119 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46087.78541666667</v>
+        <v>46102.6625</v>
       </c>
       <c r="B112" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="C112" t="n">
-        <v>1.5964</v>
+        <v>1.678</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46087.78611111111</v>
+        <v>46102.66319444445</v>
       </c>
       <c r="B113" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="C113" t="n">
-        <v>1.5926</v>
+        <v>1.6787</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46087.78680555556</v>
+        <v>46102.66388888889</v>
       </c>
       <c r="B114" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="C114" t="n">
-        <v>1.593</v>
+        <v>1.6786</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46087.7875</v>
+        <v>46102.66458333333</v>
       </c>
       <c r="B115" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="C115" t="n">
-        <v>1.5939</v>
+        <v>1.6788</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46087.78819444445</v>
+        <v>46102.66527777778</v>
       </c>
       <c r="B116" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="C116" t="n">
-        <v>1.592</v>
+        <v>1.6788</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" t="n">
         <v>1.63</v>
@@ -3104,13 +3104,13 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46087.78888888889</v>
+        <v>46102.66597222222</v>
       </c>
       <c r="B117" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="C117" t="n">
-        <v>1.5839</v>
+        <v>1.6785</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
         <v>1</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" t="n">
         <v>1.63</v>
@@ -3127,13 +3127,13 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46087.78958333333</v>
+        <v>46102.66666666666</v>
       </c>
       <c r="B118" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="C118" t="n">
-        <v>1.5863</v>
+        <v>1.6788</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -3142,21 +3142,21 @@
         <v>1</v>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46087.79027777778</v>
+        <v>46102.66736111111</v>
       </c>
       <c r="B119" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="C119" t="n">
-        <v>1.5802</v>
+        <v>1.6738</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -3165,21 +3165,21 @@
         <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46087.79097222222</v>
+        <v>46102.66805555556</v>
       </c>
       <c r="B120" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="C120" t="n">
-        <v>1.58</v>
+        <v>1.6747</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -3191,18 +3191,18 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46087.79166666666</v>
+        <v>46102.66875</v>
       </c>
       <c r="B121" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="C121" t="n">
-        <v>1.5768</v>
+        <v>1.6774</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -3214,18 +3214,18 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46087.79236111111</v>
+        <v>46102.66944444444</v>
       </c>
       <c r="B122" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="C122" t="n">
-        <v>1.5775</v>
+        <v>1.6788</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -3237,18 +3237,18 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46087.79305555556</v>
+        <v>46102.67013888889</v>
       </c>
       <c r="B123" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="C123" t="n">
-        <v>1.5722</v>
+        <v>1.6792</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -3260,18 +3260,18 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46087.79375</v>
+        <v>46102.67083333333</v>
       </c>
       <c r="B124" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="C124" t="n">
-        <v>1.5682</v>
+        <v>1.6792</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -3283,110 +3283,110 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46087.79444444444</v>
+        <v>46102.67152777778</v>
       </c>
       <c r="B125" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="C125" t="n">
-        <v>1.5673</v>
+        <v>1.6788</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" t="n">
         <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46087.79513888889</v>
+        <v>46102.67222222222</v>
       </c>
       <c r="B126" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="C126" t="n">
-        <v>1.5671</v>
+        <v>1.6777</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46087.79583333333</v>
+        <v>46102.67291666667</v>
       </c>
       <c r="B127" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="C127" t="n">
-        <v>1.5642</v>
+        <v>1.6777</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46087.79652777778</v>
+        <v>46102.67361111111</v>
       </c>
       <c r="B128" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="C128" t="n">
-        <v>1.5632</v>
+        <v>1.6781</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46087.79722222222</v>
+        <v>46102.67430555556</v>
       </c>
       <c r="B129" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="C129" t="n">
-        <v>1.562</v>
+        <v>1.6781</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -3398,18 +3398,18 @@
         <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46087.79791666667</v>
+        <v>46102.675</v>
       </c>
       <c r="B130" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="C130" t="n">
-        <v>1.5568</v>
+        <v>1.6781</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -3421,18 +3421,18 @@
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46087.79861111111</v>
+        <v>46102.67569444444</v>
       </c>
       <c r="B131" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="C131" t="n">
-        <v>1.5567</v>
+        <v>1.6781</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -3444,18 +3444,18 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46087.79930555556</v>
+        <v>46102.67638888889</v>
       </c>
       <c r="B132" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="C132" t="n">
-        <v>1.553</v>
+        <v>1.6777</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -3467,18 +3467,18 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46087.8</v>
+        <v>46102.67708333334</v>
       </c>
       <c r="B133" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="C133" t="n">
-        <v>1.5533</v>
+        <v>1.6777</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -3490,87 +3490,87 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46087.80069444444</v>
+        <v>46102.67777777778</v>
       </c>
       <c r="B134" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="C134" t="n">
-        <v>1.5517</v>
+        <v>1.6788</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F134" t="n">
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46087.80138888889</v>
+        <v>46102.67847222222</v>
       </c>
       <c r="B135" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="C135" t="n">
-        <v>1.5506</v>
+        <v>1.6788</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" t="n">
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46087.80208333334</v>
+        <v>46102.67916666667</v>
       </c>
       <c r="B136" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="C136" t="n">
-        <v>1.5509</v>
+        <v>1.6792</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46087.80277777778</v>
+        <v>46102.67986111111</v>
       </c>
       <c r="B137" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="C137" t="n">
-        <v>1.5504</v>
+        <v>1.6792</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -3579,21 +3579,21 @@
         <v>1</v>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46087.80347222222</v>
+        <v>46102.68055555555</v>
       </c>
       <c r="B138" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="C138" t="n">
-        <v>1.5519</v>
+        <v>1.6788</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -3602,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138" t="n">
         <v>1.63</v>
@@ -3610,13 +3610,13 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46087.80416666667</v>
+        <v>46102.68125</v>
       </c>
       <c r="B139" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="C139" t="n">
-        <v>1.5524</v>
+        <v>1.6788</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>1</v>
       </c>
       <c r="F139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G139" t="n">
         <v>1.63</v>
@@ -3633,13 +3633,13 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46087.80486111111</v>
+        <v>46102.68194444444</v>
       </c>
       <c r="B140" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="C140" t="n">
-        <v>1.5512</v>
+        <v>1.6793</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -3648,21 +3648,21 @@
         <v>1</v>
       </c>
       <c r="F140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46087.80555555555</v>
+        <v>46102.68263888889</v>
       </c>
       <c r="B141" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="C141" t="n">
-        <v>1.5509</v>
+        <v>1.6738</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -3674,18 +3674,18 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46087.80625</v>
+        <v>46102.68333333333</v>
       </c>
       <c r="B142" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="C142" t="n">
-        <v>1.559</v>
+        <v>1.6776</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -3697,18 +3697,18 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46087.80694444444</v>
+        <v>46102.68402777778</v>
       </c>
       <c r="B143" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="C143" t="n">
-        <v>1.56</v>
+        <v>1.6792</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -3720,18 +3720,18 @@
         <v>1</v>
       </c>
       <c r="G143" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46087.80763888889</v>
+        <v>46102.68472222222</v>
       </c>
       <c r="B144" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="C144" t="n">
-        <v>1.56</v>
+        <v>1.6792</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -3743,18 +3743,18 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46087.80833333333</v>
+        <v>46102.68541666667</v>
       </c>
       <c r="B145" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="C145" t="n">
-        <v>1.5601</v>
+        <v>1.6788</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
@@ -3766,18 +3766,18 @@
         <v>1</v>
       </c>
       <c r="G145" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46087.80902777778</v>
+        <v>46102.68611111111</v>
       </c>
       <c r="B146" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="C146" t="n">
-        <v>1.5598</v>
+        <v>1.6788</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
@@ -3789,50 +3789,50 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46087.80972222222</v>
+        <v>46102.68680555555</v>
       </c>
       <c r="B147" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="C147" t="n">
-        <v>1.5599</v>
+        <v>1.6777</v>
       </c>
       <c r="D147" t="n">
         <v>0</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" t="n">
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46087.81041666667</v>
+        <v>46102.6875</v>
       </c>
       <c r="B148" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="C148" t="n">
-        <v>1.5606</v>
+        <v>1.6777</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148" t="n">
         <v>1.67</v>
@@ -3840,13 +3840,13 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46087.81111111111</v>
+        <v>46102.68819444445</v>
       </c>
       <c r="B149" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="C149" t="n">
-        <v>1.5616</v>
+        <v>1.6781</v>
       </c>
       <c r="D149" t="n">
         <v>0</v>
@@ -3855,21 +3855,21 @@
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46087.81180555555</v>
+        <v>46102.68888888889</v>
       </c>
       <c r="B150" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="C150" t="n">
-        <v>1.5696</v>
+        <v>1.6781</v>
       </c>
       <c r="D150" t="n">
         <v>0</v>
@@ -3881,18 +3881,18 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46087.8125</v>
+        <v>46102.68958333333</v>
       </c>
       <c r="B151" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="C151" t="n">
-        <v>1.57</v>
+        <v>1.6781</v>
       </c>
       <c r="D151" t="n">
         <v>0</v>
@@ -3904,18 +3904,18 @@
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46087.81319444445</v>
+        <v>46102.69027777778</v>
       </c>
       <c r="B152" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="C152" t="n">
-        <v>1.5706</v>
+        <v>1.6777</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
@@ -3927,18 +3927,18 @@
         <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46087.81388888889</v>
+        <v>46102.69097222222</v>
       </c>
       <c r="B153" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="C153" t="n">
-        <v>1.57</v>
+        <v>1.6777</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -3955,13 +3955,13 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46087.81458333333</v>
+        <v>46102.69166666667</v>
       </c>
       <c r="B154" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="C154" t="n">
-        <v>1.57</v>
+        <v>1.6788</v>
       </c>
       <c r="D154" t="n">
         <v>0</v>
@@ -3973,18 +3973,18 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46087.81527777778</v>
+        <v>46102.69236111111</v>
       </c>
       <c r="B155" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="C155" t="n">
-        <v>1.5715</v>
+        <v>1.6788</v>
       </c>
       <c r="D155" t="n">
         <v>0</v>
@@ -4001,36 +4001,36 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46087.81597222222</v>
+        <v>46102.69375</v>
       </c>
       <c r="B156" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="C156" t="n">
-        <v>1.5742</v>
+        <v>1.6792</v>
       </c>
       <c r="D156" t="n">
         <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46087.81666666667</v>
+        <v>46102.69444444445</v>
       </c>
       <c r="B157" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="C157" t="n">
-        <v>1.5772</v>
+        <v>1.6792</v>
       </c>
       <c r="D157" t="n">
         <v>0</v>
@@ -4047,13 +4047,13 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46087.81736111111</v>
+        <v>46102.69513888889</v>
       </c>
       <c r="B158" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="C158" t="n">
-        <v>1.581</v>
+        <v>1.6788</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
@@ -4070,13 +4070,13 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46087.81805555556</v>
+        <v>46102.69583333333</v>
       </c>
       <c r="B159" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="C159" t="n">
-        <v>1.5808</v>
+        <v>1.6788</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -4085,7 +4085,7 @@
         <v>1</v>
       </c>
       <c r="F159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G159" t="n">
         <v>1.63</v>
@@ -4093,13 +4093,13 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46087.81875</v>
+        <v>46102.69652777778</v>
       </c>
       <c r="B160" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="C160" t="n">
-        <v>1.58</v>
+        <v>1.6788</v>
       </c>
       <c r="D160" t="n">
         <v>0</v>
@@ -4111,18 +4111,18 @@
         <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46087.81944444445</v>
+        <v>46102.69722222222</v>
       </c>
       <c r="B161" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="C161" t="n">
-        <v>1.58</v>
+        <v>1.6788</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -4134,18 +4134,18 @@
         <v>1</v>
       </c>
       <c r="G161" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46087.82013888889</v>
+        <v>46102.69791666666</v>
       </c>
       <c r="B162" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="C162" t="n">
-        <v>1.58</v>
+        <v>1.6788</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -4157,18 +4157,18 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46087.82083333333</v>
+        <v>46102.69861111111</v>
       </c>
       <c r="B163" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="C163" t="n">
-        <v>1.5889</v>
+        <v>1.6791</v>
       </c>
       <c r="D163" t="n">
         <v>0</v>
@@ -4180,18 +4180,18 @@
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46087.82152777778</v>
+        <v>46102.69930555556</v>
       </c>
       <c r="B164" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="C164" t="n">
-        <v>1.59</v>
+        <v>1.6791</v>
       </c>
       <c r="D164" t="n">
         <v>0</v>
@@ -4203,18 +4203,18 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46087.82222222222</v>
+        <v>46102.7</v>
       </c>
       <c r="B165" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="C165" t="n">
-        <v>1.5932</v>
+        <v>1.6786</v>
       </c>
       <c r="D165" t="n">
         <v>0</v>
@@ -4231,13 +4231,13 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46087.82291666666</v>
+        <v>46102.70069444444</v>
       </c>
       <c r="B166" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="C166" t="n">
-        <v>1.5994</v>
+        <v>1.6775</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -4249,50 +4249,50 @@
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46087.82361111111</v>
+        <v>46102.70138888889</v>
       </c>
       <c r="B167" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="C167" t="n">
-        <v>1.6009</v>
+        <v>1.6775</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F167" t="n">
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46087.82430555556</v>
+        <v>46102.70208333333</v>
       </c>
       <c r="B168" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="C168" t="n">
-        <v>1.6072</v>
+        <v>1.6781</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
       </c>
       <c r="E168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G168" t="n">
         <v>1.67</v>
@@ -4300,13 +4300,13 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46087.825</v>
+        <v>46102.70277777778</v>
       </c>
       <c r="B169" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="C169" t="n">
-        <v>1.606</v>
+        <v>1.6781</v>
       </c>
       <c r="D169" t="n">
         <v>0</v>
@@ -4315,21 +4315,21 @@
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46087.82569444444</v>
+        <v>46102.70347222222</v>
       </c>
       <c r="B170" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="C170" t="n">
-        <v>1.6065</v>
+        <v>1.6781</v>
       </c>
       <c r="D170" t="n">
         <v>0</v>
@@ -4341,18 +4341,18 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46087.82638888889</v>
+        <v>46102.70416666667</v>
       </c>
       <c r="B171" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="C171" t="n">
-        <v>1.6072</v>
+        <v>1.6781</v>
       </c>
       <c r="D171" t="n">
         <v>0</v>
@@ -4364,18 +4364,18 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46087.82708333333</v>
+        <v>46102.70486111111</v>
       </c>
       <c r="B172" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="C172" t="n">
-        <v>1.6086</v>
+        <v>1.6781</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -4387,18 +4387,18 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46087.82777777778</v>
+        <v>46102.70555555556</v>
       </c>
       <c r="B173" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="C173" t="n">
-        <v>1.61</v>
+        <v>1.6775</v>
       </c>
       <c r="D173" t="n">
         <v>0</v>
@@ -4410,18 +4410,18 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46087.82847222222</v>
+        <v>46102.70625</v>
       </c>
       <c r="B174" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="C174" t="n">
-        <v>1.61</v>
+        <v>1.6776</v>
       </c>
       <c r="D174" t="n">
         <v>0</v>
@@ -4433,18 +4433,18 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46087.82916666667</v>
+        <v>46102.70694444444</v>
       </c>
       <c r="B175" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="C175" t="n">
-        <v>1.61</v>
+        <v>1.6787</v>
       </c>
       <c r="D175" t="n">
         <v>0</v>
@@ -4456,18 +4456,18 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46087.82986111111</v>
+        <v>46102.70763888889</v>
       </c>
       <c r="B176" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="C176" t="n">
-        <v>1.61</v>
+        <v>1.6787</v>
       </c>
       <c r="D176" t="n">
         <v>0</v>
@@ -4479,64 +4479,64 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46087.83055555556</v>
+        <v>46102.70833333334</v>
       </c>
       <c r="B177" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="C177" t="n">
-        <v>1.61</v>
+        <v>1.6789</v>
       </c>
       <c r="D177" t="n">
         <v>0</v>
       </c>
       <c r="E177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46087.83125</v>
+        <v>46102.70902777778</v>
       </c>
       <c r="B178" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="C178" t="n">
-        <v>1.61</v>
+        <v>1.6789</v>
       </c>
       <c r="D178" t="n">
         <v>0</v>
       </c>
       <c r="E178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F178" t="n">
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46087.83194444444</v>
+        <v>46102.70972222222</v>
       </c>
       <c r="B179" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="C179" t="n">
-        <v>1.6101</v>
+        <v>1.6793</v>
       </c>
       <c r="D179" t="n">
         <v>0</v>
@@ -4548,18 +4548,18 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46087.83263888889</v>
+        <v>46102.71041666667</v>
       </c>
       <c r="B180" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="C180" t="n">
-        <v>1.6155</v>
+        <v>1.6785</v>
       </c>
       <c r="D180" t="n">
         <v>0</v>
@@ -4568,44 +4568,44 @@
         <v>1</v>
       </c>
       <c r="F180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46087.83333333334</v>
+        <v>46102.71111111111</v>
       </c>
       <c r="B181" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1.6785</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" t="n">
         <v>1.62</v>
-      </c>
-      <c r="C181" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="D181" t="n">
-        <v>0</v>
-      </c>
-      <c r="E181" t="n">
-        <v>1</v>
-      </c>
-      <c r="F181" t="n">
-        <v>1</v>
-      </c>
-      <c r="G181" t="n">
-        <v>1.63</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46087.83402777778</v>
+        <v>46102.71180555555</v>
       </c>
       <c r="B182" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="C182" t="n">
-        <v>1.6202</v>
+        <v>1.6739</v>
       </c>
       <c r="D182" t="n">
         <v>0</v>
@@ -4617,18 +4617,18 @@
         <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46087.83472222222</v>
+        <v>46102.7125</v>
       </c>
       <c r="B183" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="C183" t="n">
-        <v>1.6207</v>
+        <v>1.6779</v>
       </c>
       <c r="D183" t="n">
         <v>0</v>
@@ -4640,18 +4640,18 @@
         <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46087.83541666667</v>
+        <v>46102.71319444444</v>
       </c>
       <c r="B184" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="C184" t="n">
-        <v>1.6203</v>
+        <v>1.6785</v>
       </c>
       <c r="D184" t="n">
         <v>0</v>
@@ -4663,18 +4663,18 @@
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46087.83611111111</v>
+        <v>46102.71388888889</v>
       </c>
       <c r="B185" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="C185" t="n">
-        <v>1.6213</v>
+        <v>1.6789</v>
       </c>
       <c r="D185" t="n">
         <v>0</v>
@@ -4686,18 +4686,18 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46087.83680555555</v>
+        <v>46102.71458333333</v>
       </c>
       <c r="B186" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="C186" t="n">
-        <v>1.6264</v>
+        <v>1.6789</v>
       </c>
       <c r="D186" t="n">
         <v>0</v>
@@ -4709,18 +4709,18 @@
         <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46087.8375</v>
+        <v>46102.71527777778</v>
       </c>
       <c r="B187" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="C187" t="n">
-        <v>1.6257</v>
+        <v>1.6786</v>
       </c>
       <c r="D187" t="n">
         <v>0</v>
@@ -4732,18 +4732,18 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46087.83819444444</v>
+        <v>46102.71597222222</v>
       </c>
       <c r="B188" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="C188" t="n">
-        <v>1.6301</v>
+        <v>1.6773</v>
       </c>
       <c r="D188" t="n">
         <v>0</v>
@@ -4755,27 +4755,27 @@
         <v>1</v>
       </c>
       <c r="G188" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46087.83888888889</v>
+        <v>46102.71666666667</v>
       </c>
       <c r="B189" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="C189" t="n">
-        <v>1.63</v>
+        <v>1.6773</v>
       </c>
       <c r="D189" t="n">
         <v>0</v>
       </c>
       <c r="E189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G189" t="n">
         <v>1.67</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46087.83958333333</v>
+        <v>46102.71736111111</v>
       </c>
       <c r="B190" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="C190" t="n">
-        <v>1.63</v>
+        <v>1.6779</v>
       </c>
       <c r="D190" t="n">
         <v>0</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G190" t="n">
         <v>1.67</v>
@@ -4806,13 +4806,13 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46087.84027777778</v>
+        <v>46102.71805555555</v>
       </c>
       <c r="B191" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="C191" t="n">
-        <v>1.6303</v>
+        <v>1.6779</v>
       </c>
       <c r="D191" t="n">
         <v>0</v>
@@ -4821,21 +4821,21 @@
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G191" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46087.84097222222</v>
+        <v>46102.71875</v>
       </c>
       <c r="B192" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="C192" t="n">
-        <v>1.6317</v>
+        <v>1.6779</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
@@ -4847,18 +4847,18 @@
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46087.84166666667</v>
+        <v>46102.71944444445</v>
       </c>
       <c r="B193" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="C193" t="n">
-        <v>1.634</v>
+        <v>1.6779</v>
       </c>
       <c r="D193" t="n">
         <v>0</v>
@@ -4875,13 +4875,13 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46087.84236111111</v>
+        <v>46102.72013888889</v>
       </c>
       <c r="B194" t="n">
         <v>1.64</v>
       </c>
       <c r="C194" t="n">
-        <v>1.6399</v>
+        <v>1.6773</v>
       </c>
       <c r="D194" t="n">
         <v>0</v>
@@ -4893,18 +4893,18 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46087.84305555555</v>
+        <v>46102.72083333333</v>
       </c>
       <c r="B195" t="n">
         <v>1.64</v>
       </c>
       <c r="C195" t="n">
-        <v>1.64</v>
+        <v>1.6773</v>
       </c>
       <c r="D195" t="n">
         <v>0</v>
@@ -4916,18 +4916,18 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46087.84375</v>
+        <v>46102.72152777778</v>
       </c>
       <c r="B196" t="n">
         <v>1.64</v>
       </c>
       <c r="C196" t="n">
-        <v>1.64</v>
+        <v>1.6774</v>
       </c>
       <c r="D196" t="n">
         <v>0</v>
@@ -4939,18 +4939,18 @@
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46087.84444444445</v>
+        <v>46102.72222222222</v>
       </c>
       <c r="B197" t="n">
         <v>1.64</v>
       </c>
       <c r="C197" t="n">
-        <v>1.6401</v>
+        <v>1.6787</v>
       </c>
       <c r="D197" t="n">
         <v>0</v>
@@ -4967,19 +4967,19 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46087.84513888889</v>
+        <v>46102.72291666667</v>
       </c>
       <c r="B198" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="C198" t="n">
-        <v>1.6426</v>
+        <v>1.6789</v>
       </c>
       <c r="D198" t="n">
         <v>0</v>
       </c>
       <c r="E198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F198" t="n">
         <v>0</v>
@@ -4990,42 +4990,42 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46087.84583333333</v>
+        <v>46102.72361111111</v>
       </c>
       <c r="B199" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="C199" t="n">
-        <v>1.6488</v>
+        <v>1.6789</v>
       </c>
       <c r="D199" t="n">
         <v>0</v>
       </c>
       <c r="E199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F199" t="n">
         <v>0</v>
       </c>
       <c r="G199" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46087.84652777778</v>
+        <v>46102.72430555556</v>
       </c>
       <c r="B200" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="C200" t="n">
-        <v>1.6507</v>
+        <v>1.6789</v>
       </c>
       <c r="D200" t="n">
         <v>0</v>
       </c>
       <c r="E200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F200" t="n">
         <v>0</v>
@@ -5036,13 +5036,13 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46087.84722222222</v>
+        <v>46102.725</v>
       </c>
       <c r="B201" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="C201" t="n">
-        <v>1.6509</v>
+        <v>1.6793</v>
       </c>
       <c r="D201" t="n">
         <v>0</v>
@@ -5059,13 +5059,13 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46087.84791666667</v>
+        <v>46102.72569444445</v>
       </c>
       <c r="B202" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="C202" t="n">
-        <v>1.6502</v>
+        <v>1.6785</v>
       </c>
       <c r="D202" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
         <v>1</v>
       </c>
       <c r="F202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G202" t="n">
         <v>1.63</v>
@@ -5082,13 +5082,13 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46087.84861111111</v>
+        <v>46102.72638888889</v>
       </c>
       <c r="B203" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="C203" t="n">
-        <v>1.6507</v>
+        <v>1.6785</v>
       </c>
       <c r="D203" t="n">
         <v>0</v>
@@ -5097,21 +5097,21 @@
         <v>1</v>
       </c>
       <c r="F203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46087.84930555556</v>
+        <v>46102.72708333333</v>
       </c>
       <c r="B204" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="C204" t="n">
-        <v>1.6518</v>
+        <v>1.6739</v>
       </c>
       <c r="D204" t="n">
         <v>0</v>
@@ -5123,18 +5123,18 @@
         <v>1</v>
       </c>
       <c r="G204" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46087.85</v>
+        <v>46102.72777777778</v>
       </c>
       <c r="B205" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="C205" t="n">
-        <v>1.6532</v>
+        <v>1.6773</v>
       </c>
       <c r="D205" t="n">
         <v>0</v>
@@ -5146,18 +5146,18 @@
         <v>1</v>
       </c>
       <c r="G205" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46087.85069444445</v>
+        <v>46102.72847222222</v>
       </c>
       <c r="B206" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="C206" t="n">
-        <v>1.6557</v>
+        <v>1.6785</v>
       </c>
       <c r="D206" t="n">
         <v>0</v>
@@ -5169,18 +5169,18 @@
         <v>1</v>
       </c>
       <c r="G206" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46087.85138888889</v>
+        <v>46102.72916666666</v>
       </c>
       <c r="B207" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="C207" t="n">
-        <v>1.6567</v>
+        <v>1.6789</v>
       </c>
       <c r="D207" t="n">
         <v>0</v>
@@ -5192,18 +5192,18 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46087.85208333333</v>
+        <v>46102.72986111111</v>
       </c>
       <c r="B208" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="C208" t="n">
-        <v>1.6586</v>
+        <v>1.6789</v>
       </c>
       <c r="D208" t="n">
         <v>0</v>
@@ -5215,73 +5215,73 @@
         <v>1</v>
       </c>
       <c r="G208" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46087.85277777778</v>
+        <v>46102.73055555556</v>
       </c>
       <c r="B209" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="C209" t="n">
-        <v>1.6622</v>
+        <v>1.6787</v>
       </c>
       <c r="D209" t="n">
         <v>0</v>
       </c>
       <c r="E209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F209" t="n">
         <v>1</v>
       </c>
       <c r="G209" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46087.85347222222</v>
+        <v>46102.73125</v>
       </c>
       <c r="B210" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="C210" t="n">
-        <v>1.6601</v>
+        <v>1.6774</v>
       </c>
       <c r="D210" t="n">
         <v>0</v>
       </c>
       <c r="E210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G210" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46087.85416666666</v>
+        <v>46102.73194444444</v>
       </c>
       <c r="B211" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="C211" t="n">
-        <v>1.6642</v>
+        <v>1.6774</v>
       </c>
       <c r="D211" t="n">
         <v>0</v>
       </c>
       <c r="E211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G211" t="n">
         <v>1.67</v>
@@ -5289,36 +5289,36 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46087.85486111111</v>
+        <v>46102.73263888889</v>
       </c>
       <c r="B212" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="C212" t="n">
-        <v>1.6653</v>
+        <v>1.6779</v>
       </c>
       <c r="D212" t="n">
         <v>0</v>
       </c>
       <c r="E212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G212" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46087.85555555556</v>
+        <v>46102.73333333333</v>
       </c>
       <c r="B213" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="C213" t="n">
-        <v>1.6694</v>
+        <v>1.6779</v>
       </c>
       <c r="D213" t="n">
         <v>0</v>
@@ -5327,21 +5327,21 @@
         <v>0</v>
       </c>
       <c r="F213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G213" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46087.85625</v>
+        <v>46102.73402777778</v>
       </c>
       <c r="B214" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="C214" t="n">
-        <v>1.67</v>
+        <v>1.6779</v>
       </c>
       <c r="D214" t="n">
         <v>0</v>
@@ -5353,18 +5353,18 @@
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46087.85694444444</v>
+        <v>46102.73472222222</v>
       </c>
       <c r="B215" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="C215" t="n">
-        <v>1.67</v>
+        <v>1.6779</v>
       </c>
       <c r="D215" t="n">
         <v>0</v>
@@ -5376,18 +5376,18 @@
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46087.85763888889</v>
+        <v>46102.73541666667</v>
       </c>
       <c r="B216" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="C216" t="n">
-        <v>1.6703</v>
+        <v>1.6779</v>
       </c>
       <c r="D216" t="n">
         <v>0</v>
@@ -5399,18 +5399,18 @@
         <v>0</v>
       </c>
       <c r="G216" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46087.85833333333</v>
+        <v>46102.73611111111</v>
       </c>
       <c r="B217" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="C217" t="n">
-        <v>1.671</v>
+        <v>1.6775</v>
       </c>
       <c r="D217" t="n">
         <v>0</v>
@@ -5422,18 +5422,18 @@
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46087.85902777778</v>
+        <v>46102.73680555556</v>
       </c>
       <c r="B218" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="C218" t="n">
-        <v>1.6713</v>
+        <v>1.6788</v>
       </c>
       <c r="D218" t="n">
         <v>0</v>
@@ -5445,18 +5445,18 @@
         <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46087.85972222222</v>
+        <v>46102.7375</v>
       </c>
       <c r="B219" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="C219" t="n">
-        <v>1.6754</v>
+        <v>1.6788</v>
       </c>
       <c r="D219" t="n">
         <v>0</v>
@@ -5473,10 +5473,10 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46087.86041666667</v>
+        <v>46102.73819444444</v>
       </c>
       <c r="B220" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="C220" t="n">
         <v>1.679</v>
@@ -5485,47 +5485,47 @@
         <v>0</v>
       </c>
       <c r="E220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F220" t="n">
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46087.86111111111</v>
+        <v>46102.73888888889</v>
       </c>
       <c r="B221" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="C221" t="n">
-        <v>1.6788</v>
+        <v>1.679</v>
       </c>
       <c r="D221" t="n">
         <v>0</v>
       </c>
       <c r="E221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F221" t="n">
         <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46087.86180555556</v>
+        <v>46102.73958333334</v>
       </c>
       <c r="B222" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="C222" t="n">
-        <v>1.6777</v>
+        <v>1.679</v>
       </c>
       <c r="D222" t="n">
         <v>0</v>
@@ -5542,13 +5542,13 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46087.8625</v>
+        <v>46102.74027777778</v>
       </c>
       <c r="B223" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="C223" t="n">
-        <v>1.6787</v>
+        <v>1.6785</v>
       </c>
       <c r="D223" t="n">
         <v>0</v>
@@ -5557,7 +5557,7 @@
         <v>1</v>
       </c>
       <c r="F223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G223" t="n">
         <v>1.63</v>
@@ -5565,13 +5565,13 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46087.86319444444</v>
+        <v>46102.74097222222</v>
       </c>
       <c r="B224" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="C224" t="n">
-        <v>1.6778</v>
+        <v>1.6785</v>
       </c>
       <c r="D224" t="n">
         <v>0</v>
@@ -5580,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="F224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G224" t="n">
         <v>1.63</v>
@@ -5588,13 +5588,13 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46087.86388888889</v>
+        <v>46102.74166666667</v>
       </c>
       <c r="B225" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="C225" t="n">
-        <v>1.6781</v>
+        <v>1.6785</v>
       </c>
       <c r="D225" t="n">
         <v>0</v>
@@ -5603,21 +5603,21 @@
         <v>1</v>
       </c>
       <c r="F225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46087.86458333334</v>
+        <v>46102.74236111111</v>
       </c>
       <c r="B226" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="C226" t="n">
-        <v>1.6791</v>
+        <v>1.6785</v>
       </c>
       <c r="D226" t="n">
         <v>0</v>
@@ -5629,18 +5629,18 @@
         <v>1</v>
       </c>
       <c r="G226" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46087.86527777778</v>
+        <v>46102.74305555555</v>
       </c>
       <c r="B227" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="C227" t="n">
-        <v>1.6801</v>
+        <v>1.6785</v>
       </c>
       <c r="D227" t="n">
         <v>0</v>
@@ -5652,18 +5652,18 @@
         <v>1</v>
       </c>
       <c r="G227" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46087.86597222222</v>
+        <v>46102.74375</v>
       </c>
       <c r="B228" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="C228" t="n">
-        <v>1.6806</v>
+        <v>1.679</v>
       </c>
       <c r="D228" t="n">
         <v>0</v>
@@ -5675,18 +5675,18 @@
         <v>1</v>
       </c>
       <c r="G228" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46087.86666666667</v>
+        <v>46102.74444444444</v>
       </c>
       <c r="B229" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="C229" t="n">
-        <v>1.6819</v>
+        <v>1.6789</v>
       </c>
       <c r="D229" t="n">
         <v>0</v>
@@ -5698,18 +5698,18 @@
         <v>1</v>
       </c>
       <c r="G229" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46087.86736111111</v>
+        <v>46102.74513888889</v>
       </c>
       <c r="B230" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="C230" t="n">
-        <v>1.6802</v>
+        <v>1.6787</v>
       </c>
       <c r="D230" t="n">
         <v>0</v>
@@ -5721,73 +5721,73 @@
         <v>1</v>
       </c>
       <c r="G230" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46087.86805555555</v>
+        <v>46102.74583333333</v>
       </c>
       <c r="B231" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="C231" t="n">
-        <v>1.68</v>
+        <v>1.6787</v>
       </c>
       <c r="D231" t="n">
         <v>0</v>
       </c>
       <c r="E231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F231" t="n">
         <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46087.86875</v>
+        <v>46102.74652777778</v>
       </c>
       <c r="B232" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="C232" t="n">
-        <v>1.6799</v>
+        <v>1.6774</v>
       </c>
       <c r="D232" t="n">
         <v>0</v>
       </c>
       <c r="E232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G232" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46087.86944444444</v>
+        <v>46102.74722222222</v>
       </c>
       <c r="B233" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="C233" t="n">
-        <v>1.6798</v>
+        <v>1.6774</v>
       </c>
       <c r="D233" t="n">
         <v>0</v>
       </c>
       <c r="E233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G233" t="n">
         <v>1.67</v>
@@ -5795,13 +5795,13 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46087.87013888889</v>
+        <v>46102.74791666667</v>
       </c>
       <c r="B234" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="C234" t="n">
-        <v>1.6774</v>
+        <v>1.6779</v>
       </c>
       <c r="D234" t="n">
         <v>0</v>
@@ -5810,21 +5810,21 @@
         <v>0</v>
       </c>
       <c r="F234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46087.87083333333</v>
+        <v>46102.74861111111</v>
       </c>
       <c r="B235" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="C235" t="n">
-        <v>1.6797</v>
+        <v>1.6779</v>
       </c>
       <c r="D235" t="n">
         <v>0</v>
@@ -5836,15 +5836,15 @@
         <v>0</v>
       </c>
       <c r="G235" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46087.87152777778</v>
+        <v>46102.74930555555</v>
       </c>
       <c r="B236" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="C236" t="n">
         <v>1.6779</v>
@@ -5859,18 +5859,18 @@
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46087.87222222222</v>
+        <v>46102.75</v>
       </c>
       <c r="B237" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="C237" t="n">
-        <v>1.6767</v>
+        <v>1.678</v>
       </c>
       <c r="D237" t="n">
         <v>0</v>
@@ -5882,18 +5882,18 @@
         <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46087.87291666667</v>
+        <v>46102.75069444445</v>
       </c>
       <c r="B238" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="C238" t="n">
-        <v>1.6758</v>
+        <v>1.6775</v>
       </c>
       <c r="D238" t="n">
         <v>0</v>
@@ -5905,18 +5905,18 @@
         <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46087.87361111111</v>
+        <v>46102.75138888889</v>
       </c>
       <c r="B239" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="C239" t="n">
-        <v>1.6739</v>
+        <v>1.6786</v>
       </c>
       <c r="D239" t="n">
         <v>0</v>
@@ -5928,24 +5928,24 @@
         <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46087.87430555555</v>
+        <v>46102.75208333333</v>
       </c>
       <c r="B240" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="C240" t="n">
-        <v>1.6709</v>
+        <v>1.6786</v>
       </c>
       <c r="D240" t="n">
         <v>0</v>
       </c>
       <c r="E240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F240" t="n">
         <v>0</v>
@@ -5956,25 +5956,2693 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46087.875</v>
+        <v>46102.75277777778</v>
       </c>
       <c r="B241" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="C241" t="n">
-        <v>1.6645</v>
+        <v>1.6784</v>
       </c>
       <c r="D241" t="n">
         <v>0</v>
       </c>
       <c r="E241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F241" t="n">
         <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>46102.75347222222</v>
+      </c>
+      <c r="B242" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C242" t="n">
+        <v>1.6784</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
+      <c r="F242" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>46102.75416666667</v>
+      </c>
+      <c r="B243" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C243" t="n">
+        <v>1.6783</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="n">
+        <v>1</v>
+      </c>
+      <c r="F243" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>46102.75486111111</v>
+      </c>
+      <c r="B244" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C244" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" t="n">
+        <v>1</v>
+      </c>
+      <c r="F244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>46102.75555555556</v>
+      </c>
+      <c r="B245" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C245" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" t="n">
+        <v>1</v>
+      </c>
+      <c r="F245" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>46102.75625</v>
+      </c>
+      <c r="B246" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C246" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" t="n">
+        <v>1</v>
+      </c>
+      <c r="F246" t="n">
+        <v>1</v>
+      </c>
+      <c r="G246" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>46102.75694444445</v>
+      </c>
+      <c r="B247" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C247" t="n">
+        <v>1.674</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" t="n">
+        <v>1</v>
+      </c>
+      <c r="F247" t="n">
+        <v>1</v>
+      </c>
+      <c r="G247" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46102.75763888889</v>
+      </c>
+      <c r="B248" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C248" t="n">
+        <v>1.6771</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0</v>
+      </c>
+      <c r="E248" t="n">
+        <v>1</v>
+      </c>
+      <c r="F248" t="n">
+        <v>1</v>
+      </c>
+      <c r="G248" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>46102.75833333333</v>
+      </c>
+      <c r="B249" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C249" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0</v>
+      </c>
+      <c r="E249" t="n">
+        <v>1</v>
+      </c>
+      <c r="F249" t="n">
+        <v>1</v>
+      </c>
+      <c r="G249" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>46102.75902777778</v>
+      </c>
+      <c r="B250" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C250" t="n">
+        <v>1.6784</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" t="n">
+        <v>1</v>
+      </c>
+      <c r="F250" t="n">
+        <v>1</v>
+      </c>
+      <c r="G250" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>46102.75972222222</v>
+      </c>
+      <c r="B251" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C251" t="n">
+        <v>1.6786</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" t="n">
+        <v>1</v>
+      </c>
+      <c r="F251" t="n">
+        <v>1</v>
+      </c>
+      <c r="G251" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46102.76041666666</v>
+      </c>
+      <c r="B252" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C252" t="n">
+        <v>1.6786</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0</v>
+      </c>
+      <c r="E252" t="n">
+        <v>1</v>
+      </c>
+      <c r="F252" t="n">
+        <v>1</v>
+      </c>
+      <c r="G252" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>46102.76111111111</v>
+      </c>
+      <c r="B253" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C253" t="n">
+        <v>1.6775</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
+        <v>1</v>
+      </c>
+      <c r="F253" t="n">
+        <v>1</v>
+      </c>
+      <c r="G253" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
+        <v>46102.76180555556</v>
+      </c>
+      <c r="B254" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C254" t="n">
+        <v>1.6775</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>1</v>
+      </c>
+      <c r="F254" t="n">
+        <v>1</v>
+      </c>
+      <c r="G254" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>46102.7625</v>
+      </c>
+      <c r="B255" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C255" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" t="n">
+        <v>1</v>
+      </c>
+      <c r="G255" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>46102.76319444444</v>
+      </c>
+      <c r="B256" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C256" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>46102.76388888889</v>
+      </c>
+      <c r="B257" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C257" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>46102.76458333333</v>
+      </c>
+      <c r="B258" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C258" t="n">
+        <v>1.6775</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>46102.76527777778</v>
+      </c>
+      <c r="B259" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C259" t="n">
+        <v>1.6775</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0</v>
+      </c>
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>46102.76597222222</v>
+      </c>
+      <c r="B260" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C260" t="n">
+        <v>1.6786</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>46102.76666666667</v>
+      </c>
+      <c r="B261" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C261" t="n">
+        <v>1.6786</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" t="n">
+        <v>0</v>
+      </c>
+      <c r="F261" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>46102.76736111111</v>
+      </c>
+      <c r="B262" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C262" t="n">
+        <v>1.6784</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>46102.76805555556</v>
+      </c>
+      <c r="B263" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C263" t="n">
+        <v>1.6784</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0</v>
+      </c>
+      <c r="E263" t="n">
+        <v>0</v>
+      </c>
+      <c r="F263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="n">
+        <v>46102.76875</v>
+      </c>
+      <c r="B264" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C264" t="n">
+        <v>1.6784</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" t="n">
+        <v>1</v>
+      </c>
+      <c r="F264" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n">
+        <v>46102.76944444444</v>
+      </c>
+      <c r="B265" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C265" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0</v>
+      </c>
+      <c r="E265" t="n">
+        <v>1</v>
+      </c>
+      <c r="F265" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>46102.77013888889</v>
+      </c>
+      <c r="B266" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C266" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" t="n">
+        <v>1</v>
+      </c>
+      <c r="F266" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>46102.77083333334</v>
+      </c>
+      <c r="B267" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C267" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" t="n">
+        <v>1</v>
+      </c>
+      <c r="F267" t="n">
+        <v>1</v>
+      </c>
+      <c r="G267" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>46102.77152777778</v>
+      </c>
+      <c r="B268" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C268" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" t="n">
+        <v>1</v>
+      </c>
+      <c r="F268" t="n">
+        <v>1</v>
+      </c>
+      <c r="G268" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>46102.77222222222</v>
+      </c>
+      <c r="B269" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C269" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" t="n">
+        <v>1</v>
+      </c>
+      <c r="F269" t="n">
+        <v>1</v>
+      </c>
+      <c r="G269" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>46102.77291666667</v>
+      </c>
+      <c r="B270" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C270" t="n">
+        <v>1.6784</v>
+      </c>
+      <c r="D270" t="n">
+        <v>0</v>
+      </c>
+      <c r="E270" t="n">
+        <v>1</v>
+      </c>
+      <c r="F270" t="n">
+        <v>1</v>
+      </c>
+      <c r="G270" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n">
+        <v>46102.77361111111</v>
+      </c>
+      <c r="B271" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C271" t="n">
+        <v>1.6784</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" t="n">
+        <v>1</v>
+      </c>
+      <c r="F271" t="n">
+        <v>1</v>
+      </c>
+      <c r="G271" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n">
+        <v>46102.77430555555</v>
+      </c>
+      <c r="B272" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C272" t="n">
+        <v>1.6786</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0</v>
+      </c>
+      <c r="E272" t="n">
+        <v>1</v>
+      </c>
+      <c r="F272" t="n">
+        <v>1</v>
+      </c>
+      <c r="G272" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n">
+        <v>46102.775</v>
+      </c>
+      <c r="B273" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C273" t="n">
+        <v>1.6786</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" t="n">
+        <v>1</v>
+      </c>
+      <c r="F273" t="n">
+        <v>1</v>
+      </c>
+      <c r="G273" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="n">
+        <v>46102.77569444444</v>
+      </c>
+      <c r="B274" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C274" t="n">
+        <v>1.6775</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0</v>
+      </c>
+      <c r="E274" t="n">
+        <v>1</v>
+      </c>
+      <c r="F274" t="n">
+        <v>1</v>
+      </c>
+      <c r="G274" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="n">
+        <v>46102.77638888889</v>
+      </c>
+      <c r="B275" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C275" t="n">
+        <v>1.6775</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" t="n">
+        <v>1</v>
+      </c>
+      <c r="F275" t="n">
+        <v>1</v>
+      </c>
+      <c r="G275" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="n">
+        <v>46102.77708333333</v>
+      </c>
+      <c r="B276" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C276" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>1</v>
+      </c>
+      <c r="G276" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="n">
+        <v>46102.77777777778</v>
+      </c>
+      <c r="B277" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C277" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="n">
+        <v>46102.77847222222</v>
+      </c>
+      <c r="B278" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C278" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="n">
+        <v>46102.77916666667</v>
+      </c>
+      <c r="B279" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C279" t="n">
+        <v>1.6775</v>
+      </c>
+      <c r="D279" t="n">
+        <v>0</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="n">
+        <v>46102.77986111111</v>
+      </c>
+      <c r="B280" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C280" t="n">
+        <v>1.6775</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="n">
+        <v>46102.78055555555</v>
+      </c>
+      <c r="B281" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C281" t="n">
+        <v>1.6775</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="n">
+        <v>46102.78125</v>
+      </c>
+      <c r="B282" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C282" t="n">
+        <v>1.6786</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0</v>
+      </c>
+      <c r="F282" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="n">
+        <v>46102.78194444445</v>
+      </c>
+      <c r="B283" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C283" t="n">
+        <v>1.6784</v>
+      </c>
+      <c r="D283" t="n">
+        <v>0</v>
+      </c>
+      <c r="E283" t="n">
+        <v>0</v>
+      </c>
+      <c r="F283" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="n">
+        <v>46102.78263888889</v>
+      </c>
+      <c r="B284" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C284" t="n">
+        <v>1.6784</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0</v>
+      </c>
+      <c r="F284" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="n">
+        <v>46102.78333333333</v>
+      </c>
+      <c r="B285" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C285" t="n">
+        <v>1.6784</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" t="n">
+        <v>1</v>
+      </c>
+      <c r="F285" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="n">
+        <v>46102.78402777778</v>
+      </c>
+      <c r="B286" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C286" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D286" t="n">
+        <v>0</v>
+      </c>
+      <c r="E286" t="n">
+        <v>1</v>
+      </c>
+      <c r="F286" t="n">
+        <v>0</v>
+      </c>
+      <c r="G286" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="n">
+        <v>46102.78472222222</v>
+      </c>
+      <c r="B287" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="C287" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D287" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" t="n">
+        <v>1</v>
+      </c>
+      <c r="F287" t="n">
+        <v>0</v>
+      </c>
+      <c r="G287" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="n">
+        <v>46102.78541666667</v>
+      </c>
+      <c r="B288" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="C288" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0</v>
+      </c>
+      <c r="E288" t="n">
+        <v>1</v>
+      </c>
+      <c r="F288" t="n">
+        <v>0</v>
+      </c>
+      <c r="G288" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="n">
+        <v>46102.78611111111</v>
+      </c>
+      <c r="B289" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="C289" t="n">
+        <v>1.674</v>
+      </c>
+      <c r="D289" t="n">
+        <v>0</v>
+      </c>
+      <c r="E289" t="n">
+        <v>1</v>
+      </c>
+      <c r="F289" t="n">
+        <v>1</v>
+      </c>
+      <c r="G289" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="n">
+        <v>46102.78680555556</v>
+      </c>
+      <c r="B290" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="C290" t="n">
+        <v>1.6776</v>
+      </c>
+      <c r="D290" t="n">
+        <v>0</v>
+      </c>
+      <c r="E290" t="n">
+        <v>1</v>
+      </c>
+      <c r="F290" t="n">
+        <v>1</v>
+      </c>
+      <c r="G290" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="n">
+        <v>46102.7875</v>
+      </c>
+      <c r="B291" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="C291" t="n">
+        <v>1.6784</v>
+      </c>
+      <c r="D291" t="n">
+        <v>0</v>
+      </c>
+      <c r="E291" t="n">
+        <v>1</v>
+      </c>
+      <c r="F291" t="n">
+        <v>1</v>
+      </c>
+      <c r="G291" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="n">
+        <v>46102.78819444445</v>
+      </c>
+      <c r="B292" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="C292" t="n">
+        <v>1.6784</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" t="n">
+        <v>1</v>
+      </c>
+      <c r="F292" t="n">
+        <v>1</v>
+      </c>
+      <c r="G292" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="n">
+        <v>46102.78888888889</v>
+      </c>
+      <c r="B293" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="C293" t="n">
+        <v>1.6786</v>
+      </c>
+      <c r="D293" t="n">
+        <v>0</v>
+      </c>
+      <c r="E293" t="n">
+        <v>1</v>
+      </c>
+      <c r="F293" t="n">
+        <v>1</v>
+      </c>
+      <c r="G293" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="n">
+        <v>46102.78958333333</v>
+      </c>
+      <c r="B294" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C294" t="n">
+        <v>1.6786</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0</v>
+      </c>
+      <c r="E294" t="n">
+        <v>1</v>
+      </c>
+      <c r="F294" t="n">
+        <v>1</v>
+      </c>
+      <c r="G294" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="n">
+        <v>46102.79027777778</v>
+      </c>
+      <c r="B295" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C295" t="n">
+        <v>1.6775</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0</v>
+      </c>
+      <c r="E295" t="n">
+        <v>1</v>
+      </c>
+      <c r="F295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G295" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="n">
+        <v>46102.79097222222</v>
+      </c>
+      <c r="B296" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C296" t="n">
+        <v>1.6775</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" t="n">
+        <v>1</v>
+      </c>
+      <c r="F296" t="n">
+        <v>1</v>
+      </c>
+      <c r="G296" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="n">
+        <v>46102.79166666666</v>
+      </c>
+      <c r="B297" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C297" t="n">
+        <v>1.6773</v>
+      </c>
+      <c r="D297" t="n">
+        <v>0</v>
+      </c>
+      <c r="E297" t="n">
+        <v>0</v>
+      </c>
+      <c r="F297" t="n">
+        <v>1</v>
+      </c>
+      <c r="G297" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="n">
+        <v>46102.79236111111</v>
+      </c>
+      <c r="B298" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C298" t="n">
+        <v>1.6773</v>
+      </c>
+      <c r="D298" t="n">
+        <v>0</v>
+      </c>
+      <c r="E298" t="n">
+        <v>0</v>
+      </c>
+      <c r="F298" t="n">
+        <v>0</v>
+      </c>
+      <c r="G298" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="n">
+        <v>46102.79305555556</v>
+      </c>
+      <c r="B299" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C299" t="n">
+        <v>1.6773</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" t="n">
+        <v>0</v>
+      </c>
+      <c r="F299" t="n">
+        <v>0</v>
+      </c>
+      <c r="G299" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="n">
+        <v>46102.79375</v>
+      </c>
+      <c r="B300" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C300" t="n">
+        <v>1.6775</v>
+      </c>
+      <c r="D300" t="n">
+        <v>0</v>
+      </c>
+      <c r="E300" t="n">
+        <v>0</v>
+      </c>
+      <c r="F300" t="n">
+        <v>0</v>
+      </c>
+      <c r="G300" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="n">
+        <v>46102.79444444444</v>
+      </c>
+      <c r="B301" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C301" t="n">
+        <v>1.6775</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0</v>
+      </c>
+      <c r="E301" t="n">
+        <v>0</v>
+      </c>
+      <c r="F301" t="n">
+        <v>0</v>
+      </c>
+      <c r="G301" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="n">
+        <v>46102.79513888889</v>
+      </c>
+      <c r="B302" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C302" t="n">
+        <v>1.6792</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" t="n">
+        <v>0</v>
+      </c>
+      <c r="F302" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="n">
+        <v>46102.79583333333</v>
+      </c>
+      <c r="B303" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C303" t="n">
+        <v>1.6792</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0</v>
+      </c>
+      <c r="E303" t="n">
+        <v>0</v>
+      </c>
+      <c r="F303" t="n">
+        <v>0</v>
+      </c>
+      <c r="G303" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="n">
+        <v>46102.79652777778</v>
+      </c>
+      <c r="B304" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C304" t="n">
+        <v>1.6793</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0</v>
+      </c>
+      <c r="E304" t="n">
+        <v>0</v>
+      </c>
+      <c r="F304" t="n">
+        <v>0</v>
+      </c>
+      <c r="G304" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="n">
+        <v>46102.79722222222</v>
+      </c>
+      <c r="B305" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C305" t="n">
+        <v>1.6793</v>
+      </c>
+      <c r="D305" t="n">
+        <v>0</v>
+      </c>
+      <c r="E305" t="n">
+        <v>0</v>
+      </c>
+      <c r="F305" t="n">
+        <v>0</v>
+      </c>
+      <c r="G305" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="n">
+        <v>46102.79791666667</v>
+      </c>
+      <c r="B306" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C306" t="n">
+        <v>1.6793</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" t="n">
+        <v>1</v>
+      </c>
+      <c r="F306" t="n">
+        <v>0</v>
+      </c>
+      <c r="G306" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="n">
+        <v>46102.79861111111</v>
+      </c>
+      <c r="B307" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C307" t="n">
+        <v>1.6796</v>
+      </c>
+      <c r="D307" t="n">
+        <v>0</v>
+      </c>
+      <c r="E307" t="n">
+        <v>1</v>
+      </c>
+      <c r="F307" t="n">
+        <v>0</v>
+      </c>
+      <c r="G307" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="n">
+        <v>46102.79930555556</v>
+      </c>
+      <c r="B308" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C308" t="n">
+        <v>1.6789</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0</v>
+      </c>
+      <c r="E308" t="n">
+        <v>1</v>
+      </c>
+      <c r="F308" t="n">
+        <v>0</v>
+      </c>
+      <c r="G308" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="n">
+        <v>46102.8</v>
+      </c>
+      <c r="B309" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C309" t="n">
+        <v>1.6789</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0</v>
+      </c>
+      <c r="E309" t="n">
+        <v>1</v>
+      </c>
+      <c r="F309" t="n">
+        <v>1</v>
+      </c>
+      <c r="G309" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="n">
+        <v>46102.80069444444</v>
+      </c>
+      <c r="B310" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C310" t="n">
+        <v>1.6789</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0</v>
+      </c>
+      <c r="E310" t="n">
+        <v>1</v>
+      </c>
+      <c r="F310" t="n">
+        <v>1</v>
+      </c>
+      <c r="G310" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="n">
+        <v>46102.80138888889</v>
+      </c>
+      <c r="B311" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C311" t="n">
+        <v>1.6793</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0</v>
+      </c>
+      <c r="E311" t="n">
+        <v>1</v>
+      </c>
+      <c r="F311" t="n">
+        <v>1</v>
+      </c>
+      <c r="G311" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="n">
+        <v>46102.80208333334</v>
+      </c>
+      <c r="B312" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C312" t="n">
+        <v>1.6793</v>
+      </c>
+      <c r="D312" t="n">
+        <v>0</v>
+      </c>
+      <c r="E312" t="n">
+        <v>1</v>
+      </c>
+      <c r="F312" t="n">
+        <v>1</v>
+      </c>
+      <c r="G312" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="n">
+        <v>46102.80277777778</v>
+      </c>
+      <c r="B313" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C313" t="n">
+        <v>1.6792</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" t="n">
+        <v>1</v>
+      </c>
+      <c r="F313" t="n">
+        <v>1</v>
+      </c>
+      <c r="G313" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="n">
+        <v>46102.80347222222</v>
+      </c>
+      <c r="B314" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C314" t="n">
+        <v>1.6792</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0</v>
+      </c>
+      <c r="E314" t="n">
+        <v>1</v>
+      </c>
+      <c r="F314" t="n">
+        <v>1</v>
+      </c>
+      <c r="G314" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="n">
+        <v>46102.80416666667</v>
+      </c>
+      <c r="B315" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C315" t="n">
+        <v>1.6774</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0</v>
+      </c>
+      <c r="E315" t="n">
+        <v>1</v>
+      </c>
+      <c r="F315" t="n">
+        <v>1</v>
+      </c>
+      <c r="G315" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="n">
+        <v>46102.80486111111</v>
+      </c>
+      <c r="B316" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C316" t="n">
+        <v>1.6774</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0</v>
+      </c>
+      <c r="E316" t="n">
+        <v>1</v>
+      </c>
+      <c r="F316" t="n">
+        <v>1</v>
+      </c>
+      <c r="G316" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="n">
+        <v>46102.80555555555</v>
+      </c>
+      <c r="B317" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C317" t="n">
+        <v>1.6773</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0</v>
+      </c>
+      <c r="E317" t="n">
+        <v>0</v>
+      </c>
+      <c r="F317" t="n">
+        <v>1</v>
+      </c>
+      <c r="G317" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="n">
+        <v>46102.80625</v>
+      </c>
+      <c r="B318" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C318" t="n">
+        <v>1.6773</v>
+      </c>
+      <c r="D318" t="n">
+        <v>0</v>
+      </c>
+      <c r="E318" t="n">
+        <v>0</v>
+      </c>
+      <c r="F318" t="n">
+        <v>0</v>
+      </c>
+      <c r="G318" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="n">
+        <v>46102.80694444444</v>
+      </c>
+      <c r="B319" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C319" t="n">
+        <v>1.6773</v>
+      </c>
+      <c r="D319" t="n">
+        <v>0</v>
+      </c>
+      <c r="E319" t="n">
+        <v>0</v>
+      </c>
+      <c r="F319" t="n">
+        <v>0</v>
+      </c>
+      <c r="G319" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="n">
+        <v>46102.80763888889</v>
+      </c>
+      <c r="B320" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C320" t="n">
+        <v>1.6775</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0</v>
+      </c>
+      <c r="E320" t="n">
+        <v>0</v>
+      </c>
+      <c r="F320" t="n">
+        <v>0</v>
+      </c>
+      <c r="G320" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="n">
+        <v>46102.80833333333</v>
+      </c>
+      <c r="B321" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C321" t="n">
+        <v>1.6775</v>
+      </c>
+      <c r="D321" t="n">
+        <v>0</v>
+      </c>
+      <c r="E321" t="n">
+        <v>0</v>
+      </c>
+      <c r="F321" t="n">
+        <v>0</v>
+      </c>
+      <c r="G321" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="n">
+        <v>46102.80902777778</v>
+      </c>
+      <c r="B322" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C322" t="n">
+        <v>1.6775</v>
+      </c>
+      <c r="D322" t="n">
+        <v>0</v>
+      </c>
+      <c r="E322" t="n">
+        <v>0</v>
+      </c>
+      <c r="F322" t="n">
+        <v>0</v>
+      </c>
+      <c r="G322" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="n">
+        <v>46102.80972222222</v>
+      </c>
+      <c r="B323" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C323" t="n">
+        <v>1.6775</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" t="n">
+        <v>0</v>
+      </c>
+      <c r="F323" t="n">
+        <v>0</v>
+      </c>
+      <c r="G323" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="n">
+        <v>46102.81041666667</v>
+      </c>
+      <c r="B324" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C324" t="n">
+        <v>1.6792</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0</v>
+      </c>
+      <c r="E324" t="n">
+        <v>0</v>
+      </c>
+      <c r="F324" t="n">
+        <v>0</v>
+      </c>
+      <c r="G324" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="n">
+        <v>46102.81111111111</v>
+      </c>
+      <c r="B325" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C325" t="n">
+        <v>1.6792</v>
+      </c>
+      <c r="D325" t="n">
+        <v>0</v>
+      </c>
+      <c r="E325" t="n">
+        <v>0</v>
+      </c>
+      <c r="F325" t="n">
+        <v>0</v>
+      </c>
+      <c r="G325" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="n">
+        <v>46102.81180555555</v>
+      </c>
+      <c r="B326" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C326" t="n">
+        <v>1.6793</v>
+      </c>
+      <c r="D326" t="n">
+        <v>0</v>
+      </c>
+      <c r="E326" t="n">
+        <v>0</v>
+      </c>
+      <c r="F326" t="n">
+        <v>0</v>
+      </c>
+      <c r="G326" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="n">
+        <v>46102.8125</v>
+      </c>
+      <c r="B327" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C327" t="n">
+        <v>1.6793</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0</v>
+      </c>
+      <c r="E327" t="n">
+        <v>1</v>
+      </c>
+      <c r="F327" t="n">
+        <v>0</v>
+      </c>
+      <c r="G327" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="n">
+        <v>46102.81319444445</v>
+      </c>
+      <c r="B328" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C328" t="n">
+        <v>1.6789</v>
+      </c>
+      <c r="D328" t="n">
+        <v>0</v>
+      </c>
+      <c r="E328" t="n">
+        <v>1</v>
+      </c>
+      <c r="F328" t="n">
+        <v>0</v>
+      </c>
+      <c r="G328" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="n">
+        <v>46102.81388888889</v>
+      </c>
+      <c r="B329" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C329" t="n">
+        <v>1.6789</v>
+      </c>
+      <c r="D329" t="n">
+        <v>0</v>
+      </c>
+      <c r="E329" t="n">
+        <v>1</v>
+      </c>
+      <c r="F329" t="n">
+        <v>0</v>
+      </c>
+      <c r="G329" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="n">
+        <v>46102.81458333333</v>
+      </c>
+      <c r="B330" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C330" t="n">
+        <v>1.6789</v>
+      </c>
+      <c r="D330" t="n">
+        <v>0</v>
+      </c>
+      <c r="E330" t="n">
+        <v>1</v>
+      </c>
+      <c r="F330" t="n">
+        <v>0</v>
+      </c>
+      <c r="G330" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="n">
+        <v>46102.81527777778</v>
+      </c>
+      <c r="B331" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C331" t="n">
+        <v>1.6789</v>
+      </c>
+      <c r="D331" t="n">
+        <v>0</v>
+      </c>
+      <c r="E331" t="n">
+        <v>1</v>
+      </c>
+      <c r="F331" t="n">
+        <v>1</v>
+      </c>
+      <c r="G331" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="n">
+        <v>46102.81597222222</v>
+      </c>
+      <c r="B332" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C332" t="n">
+        <v>1.6789</v>
+      </c>
+      <c r="D332" t="n">
+        <v>0</v>
+      </c>
+      <c r="E332" t="n">
+        <v>1</v>
+      </c>
+      <c r="F332" t="n">
+        <v>1</v>
+      </c>
+      <c r="G332" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="n">
+        <v>46102.81666666667</v>
+      </c>
+      <c r="B333" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C333" t="n">
+        <v>1.6792</v>
+      </c>
+      <c r="D333" t="n">
+        <v>0</v>
+      </c>
+      <c r="E333" t="n">
+        <v>1</v>
+      </c>
+      <c r="F333" t="n">
+        <v>1</v>
+      </c>
+      <c r="G333" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="n">
+        <v>46102.81736111111</v>
+      </c>
+      <c r="B334" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C334" t="n">
+        <v>1.6791</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" t="n">
+        <v>1</v>
+      </c>
+      <c r="F334" t="n">
+        <v>1</v>
+      </c>
+      <c r="G334" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="n">
+        <v>46102.81805555556</v>
+      </c>
+      <c r="B335" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C335" t="n">
+        <v>1.6791</v>
+      </c>
+      <c r="D335" t="n">
+        <v>0</v>
+      </c>
+      <c r="E335" t="n">
+        <v>1</v>
+      </c>
+      <c r="F335" t="n">
+        <v>1</v>
+      </c>
+      <c r="G335" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="n">
+        <v>46102.81875</v>
+      </c>
+      <c r="B336" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C336" t="n">
+        <v>1.6773</v>
+      </c>
+      <c r="D336" t="n">
+        <v>0</v>
+      </c>
+      <c r="E336" t="n">
+        <v>1</v>
+      </c>
+      <c r="F336" t="n">
+        <v>1</v>
+      </c>
+      <c r="G336" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="n">
+        <v>46102.81944444445</v>
+      </c>
+      <c r="B337" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C337" t="n">
+        <v>1.6773</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0</v>
+      </c>
+      <c r="E337" t="n">
+        <v>1</v>
+      </c>
+      <c r="F337" t="n">
+        <v>1</v>
+      </c>
+      <c r="G337" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="n">
+        <v>46102.82013888889</v>
+      </c>
+      <c r="B338" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C338" t="n">
+        <v>1.6773</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" t="n">
+        <v>0</v>
+      </c>
+      <c r="F338" t="n">
+        <v>1</v>
+      </c>
+      <c r="G338" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="n">
+        <v>46102.82083333333</v>
+      </c>
+      <c r="B339" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C339" t="n">
+        <v>1.6773</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0</v>
+      </c>
+      <c r="E339" t="n">
+        <v>0</v>
+      </c>
+      <c r="F339" t="n">
+        <v>0</v>
+      </c>
+      <c r="G339" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="n">
+        <v>46102.82152777778</v>
+      </c>
+      <c r="B340" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C340" t="n">
+        <v>1.6773</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0</v>
+      </c>
+      <c r="E340" t="n">
+        <v>0</v>
+      </c>
+      <c r="F340" t="n">
+        <v>0</v>
+      </c>
+      <c r="G340" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="n">
+        <v>46102.82222222222</v>
+      </c>
+      <c r="B341" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C341" t="n">
+        <v>1.6773</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" t="n">
+        <v>0</v>
+      </c>
+      <c r="F341" t="n">
+        <v>0</v>
+      </c>
+      <c r="G341" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="n">
+        <v>46102.82291666666</v>
+      </c>
+      <c r="B342" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C342" t="n">
+        <v>1.6774</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0</v>
+      </c>
+      <c r="E342" t="n">
+        <v>0</v>
+      </c>
+      <c r="F342" t="n">
+        <v>0</v>
+      </c>
+      <c r="G342" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="n">
+        <v>46102.82361111111</v>
+      </c>
+      <c r="B343" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C343" t="n">
+        <v>1.6774</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0</v>
+      </c>
+      <c r="E343" t="n">
+        <v>0</v>
+      </c>
+      <c r="F343" t="n">
+        <v>0</v>
+      </c>
+      <c r="G343" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="n">
+        <v>46102.82430555556</v>
+      </c>
+      <c r="B344" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C344" t="n">
+        <v>1.6791</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0</v>
+      </c>
+      <c r="E344" t="n">
+        <v>0</v>
+      </c>
+      <c r="F344" t="n">
+        <v>0</v>
+      </c>
+      <c r="G344" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="n">
+        <v>46102.825</v>
+      </c>
+      <c r="B345" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C345" t="n">
+        <v>1.6791</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0</v>
+      </c>
+      <c r="E345" t="n">
+        <v>0</v>
+      </c>
+      <c r="F345" t="n">
+        <v>0</v>
+      </c>
+      <c r="G345" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="n">
+        <v>46102.82569444444</v>
+      </c>
+      <c r="B346" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C346" t="n">
+        <v>1.6791</v>
+      </c>
+      <c r="D346" t="n">
+        <v>0</v>
+      </c>
+      <c r="E346" t="n">
+        <v>0</v>
+      </c>
+      <c r="F346" t="n">
+        <v>0</v>
+      </c>
+      <c r="G346" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="n">
+        <v>46102.82638888889</v>
+      </c>
+      <c r="B347" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C347" t="n">
+        <v>1.6792</v>
+      </c>
+      <c r="D347" t="n">
+        <v>0</v>
+      </c>
+      <c r="E347" t="n">
+        <v>0</v>
+      </c>
+      <c r="F347" t="n">
+        <v>0</v>
+      </c>
+      <c r="G347" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="n">
+        <v>46102.82708333333</v>
+      </c>
+      <c r="B348" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C348" t="n">
+        <v>1.6792</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0</v>
+      </c>
+      <c r="E348" t="n">
+        <v>1</v>
+      </c>
+      <c r="F348" t="n">
+        <v>0</v>
+      </c>
+      <c r="G348" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="n">
+        <v>46102.82777777778</v>
+      </c>
+      <c r="B349" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C349" t="n">
+        <v>1.6795</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0</v>
+      </c>
+      <c r="E349" t="n">
+        <v>1</v>
+      </c>
+      <c r="F349" t="n">
+        <v>0</v>
+      </c>
+      <c r="G349" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="n">
+        <v>46102.82847222222</v>
+      </c>
+      <c r="B350" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C350" t="n">
+        <v>1.6789</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0</v>
+      </c>
+      <c r="E350" t="n">
+        <v>1</v>
+      </c>
+      <c r="F350" t="n">
+        <v>0</v>
+      </c>
+      <c r="G350" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="n">
+        <v>46102.82916666667</v>
+      </c>
+      <c r="B351" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C351" t="n">
+        <v>1.6789</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0</v>
+      </c>
+      <c r="E351" t="n">
+        <v>1</v>
+      </c>
+      <c r="F351" t="n">
+        <v>0</v>
+      </c>
+      <c r="G351" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="n">
+        <v>46102.82986111111</v>
+      </c>
+      <c r="B352" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C352" t="n">
+        <v>1.6789</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" t="n">
+        <v>1</v>
+      </c>
+      <c r="F352" t="n">
+        <v>1</v>
+      </c>
+      <c r="G352" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="n">
+        <v>46102.83055555556</v>
+      </c>
+      <c r="B353" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C353" t="n">
+        <v>1.6789</v>
+      </c>
+      <c r="D353" t="n">
+        <v>0</v>
+      </c>
+      <c r="E353" t="n">
+        <v>1</v>
+      </c>
+      <c r="F353" t="n">
+        <v>1</v>
+      </c>
+      <c r="G353" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="n">
+        <v>46102.83125</v>
+      </c>
+      <c r="B354" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C354" t="n">
+        <v>1.6792</v>
+      </c>
+      <c r="D354" t="n">
+        <v>0</v>
+      </c>
+      <c r="E354" t="n">
+        <v>1</v>
+      </c>
+      <c r="F354" t="n">
+        <v>1</v>
+      </c>
+      <c r="G354" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="n">
+        <v>46102.83194444444</v>
+      </c>
+      <c r="B355" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C355" t="n">
+        <v>1.6789</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0</v>
+      </c>
+      <c r="E355" t="n">
+        <v>1</v>
+      </c>
+      <c r="F355" t="n">
+        <v>1</v>
+      </c>
+      <c r="G355" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="n">
+        <v>46102.83263888889</v>
+      </c>
+      <c r="B356" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C356" t="n">
+        <v>1.6789</v>
+      </c>
+      <c r="D356" t="n">
+        <v>0</v>
+      </c>
+      <c r="E356" t="n">
+        <v>1</v>
+      </c>
+      <c r="F356" t="n">
+        <v>1</v>
+      </c>
+      <c r="G356" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="n">
+        <v>46102.83333333334</v>
+      </c>
+      <c r="B357" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C357" t="n">
+        <v>1.6773</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0</v>
+      </c>
+      <c r="E357" t="n">
+        <v>1</v>
+      </c>
+      <c r="F357" t="n">
+        <v>1</v>
+      </c>
+      <c r="G357" t="n">
+        <v>1.67</v>
       </c>
     </row>
   </sheetData>
